--- a/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="92">
   <si>
     <t>LVMUY</t>
   </si>
@@ -656,415 +656,427 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21660900</v>
+        <v>47781700</v>
       </c>
       <c r="E8" s="3">
-        <v>45830400</v>
+        <v>21722800</v>
       </c>
       <c r="F8" s="3">
-        <v>22823000</v>
+        <v>45961300</v>
       </c>
       <c r="G8" s="3">
-        <v>46063700</v>
+        <v>22888200</v>
       </c>
       <c r="H8" s="3">
-        <v>21434200</v>
+        <v>46195300</v>
       </c>
       <c r="I8" s="3">
-        <v>39851000</v>
+        <v>21495400</v>
       </c>
       <c r="J8" s="3">
+        <v>39964800</v>
+      </c>
+      <c r="K8" s="3">
         <v>19533300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>38539800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16704900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>30327600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14249300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>26189700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12408100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20065100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11963900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>33373900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16312000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>29506500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14998000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>29662400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>12603400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>23881500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>12178100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>25718300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11647400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>22118900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11601900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>23959800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10726300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3">
-        <v>14021500</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3">
-        <v>14723500</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3">
-        <v>12388500</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="D9" s="3">
+        <v>15182300</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>14061500</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3">
+        <v>14765500</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="3">
+        <v>12423900</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3">
         <v>12191800</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>9635200</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>8845900</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>7638600</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>11295900</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>9937100</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>10048700</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>7828700</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="3">
         <v>8866000</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="3">
         <v>7720400</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE9" s="3">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="3">
         <v>8359900</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3">
-        <v>31808900</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3">
-        <v>31340200</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3">
-        <v>27462400</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="D10" s="3">
+        <v>32599500</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
+        <v>31899800</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3">
+        <v>31429800</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3">
+        <v>27540900</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" s="3">
         <v>26348000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3">
         <v>20692400</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>17343800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>12426600</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>22078100</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>19569400</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>19613700</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>16052800</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="3">
         <v>16852300</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="3">
         <v>14398500</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE10" s="3">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="3">
         <v>15599900</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1097,8 +1109,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1189,8 +1202,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,100 +1297,106 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>226300</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>8700</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
-        <v>188800</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
-        <v>117200</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>189300</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>117500</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>94300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>32800</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>150600</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>136400</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>101600</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>48200</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>62700</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>80200</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="3">
         <v>150300</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
         <v>111100</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF14" s="3">
         <v>159600</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1456,8 +1478,8 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>5</v>
+      <c r="AD15" s="3">
+        <v>0</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>5</v>
@@ -1465,8 +1487,11 @@
       <c r="AF15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1496,192 +1521,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="3">
-        <v>33283500</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="3">
-        <v>34265400</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="3">
-        <v>28863200</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="D17" s="3">
+        <v>35817000</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3">
+        <v>33378600</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3">
+        <v>34363300</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3">
+        <v>28945600</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3">
         <v>28179000</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>22300500</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3">
         <v>19751500</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>18410200</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>26332100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>23341000</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>23394200</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>18854900</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="3">
         <v>20593000</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="3">
         <v>18141500</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="3">
         <v>19282200</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3">
-        <v>12546900</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="3">
-        <v>11798300</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" s="3">
-        <v>10987800</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="D18" s="3">
+        <v>11964700</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3">
+        <v>12582800</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3">
+        <v>11832000</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3">
+        <v>11019200</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3">
         <v>10360700</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>8027000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <v>6438200</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>1654900</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>7041800</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>6165500</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>6268200</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>5026600</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>5125300</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>3977500</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF18" s="3">
         <v>4677600</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,100 +1746,104 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3">
-        <v>946100</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="3">
-        <v>174700</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-723700</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="D20" s="3">
+        <v>-907500</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
+        <v>948800</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3">
+        <v>175200</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-725800</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>181000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>153400</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>4000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-268400</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>-151800</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>20000</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>-332400</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>56000</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>57200</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>66200</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-248800</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1832,350 +1868,362 @@
       <c r="J21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="3">
         <v>16862100</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>12476500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>10093400</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>8966500</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>7397900</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>6253100</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>6715100</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>5176900</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>5954700</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3">
-        <v>439400</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="3">
-        <v>272300</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="3">
-        <v>142100</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="D22" s="3">
+        <v>618000</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
+        <v>440700</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3">
+        <v>273100</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3">
+        <v>142500</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3">
         <v>110600</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3">
         <v>140700</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3">
         <v>149600</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3">
         <v>235600</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>261500</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>261200</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>100500</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="3">
         <v>80200</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB22" s="3">
         <v>102100</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="3">
         <v>87500</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF22" s="3">
         <v>63400</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="3">
-        <v>13053600</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="3">
-        <v>11700600</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="3">
-        <v>10122000</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="D23" s="3">
+        <v>10439200</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3">
+        <v>13090900</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3">
+        <v>11734100</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3">
+        <v>10150900</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="3">
         <v>10431200</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>8039700</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3">
         <v>6292600</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>1150900</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>6628600</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>5924400</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>5835200</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>5002500</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB23" s="3">
         <v>5080400</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="3">
         <v>3956100</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE23" s="3">
+      <c r="AE23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF23" s="3">
         <v>4365400</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="3">
-        <v>3395000</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="3">
-        <v>3230000</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="3">
-        <v>2587700</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="D24" s="3">
+        <v>2768100</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
+        <v>3404700</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>3239300</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3">
+        <v>2595100</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="3">
         <v>2710300</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3">
         <v>2128700</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3">
         <v>1893100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>557500</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>1752300</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>1683400</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>1460900</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3">
         <v>1387900</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB24" s="3">
         <v>1154500</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD24" s="3">
         <v>1329600</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF24" s="3">
         <v>1430900</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2266,192 +2314,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="3">
-        <v>9658700</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" s="3">
-        <v>8470600</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I26" s="3">
-        <v>7534200</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="D26" s="3">
+        <v>7671100</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3">
+        <v>9686300</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3">
+        <v>8494800</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3">
+        <v>7555800</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3">
         <v>7721000</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>5911000</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3">
         <v>4399500</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>593500</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>4876300</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>4240900</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>4374400</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>3614600</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="3">
         <v>3925800</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD26" s="3">
         <v>2626600</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF26" s="3">
         <v>2934500</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="3">
-        <v>9201900</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="3">
-        <v>8193900</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" s="3">
-        <v>7087200</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="D27" s="3">
+        <v>7282700</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3">
+        <v>9228200</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3">
+        <v>8217300</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3">
+        <v>7107500</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3">
         <v>7314400</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>5607400</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3">
         <v>4169100</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>569500</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>4556400</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>3844500</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>3962700</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>3298400</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="3">
         <v>3633000</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD27" s="3">
         <v>2386500</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF27" s="3">
         <v>2664500</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2542,8 +2599,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2634,8 +2694,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2726,8 +2789,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2818,192 +2884,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-946100</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-174700</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3">
-        <v>723700</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="D32" s="3">
+        <v>907500</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-948800</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-175200</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
+        <v>725800</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>-181000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>-153400</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>-4000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>268400</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>151800</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>-20000</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>332400</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-56000</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-57200</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-66200</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF32" s="3">
         <v>248800</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="3">
-        <v>9201900</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="3">
-        <v>8193900</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" s="3">
-        <v>7087200</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="D33" s="3">
+        <v>7282700</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3">
+        <v>9228200</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3">
+        <v>8217300</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3">
+        <v>7107500</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3">
         <v>7314400</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>5607400</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3">
         <v>4169100</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>569500</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>4556400</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>3844500</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>3962700</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>3298400</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB33" s="3">
         <v>3633000</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD33" s="3">
         <v>2386500</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF33" s="3">
         <v>2664500</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3094,197 +3169,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E35" s="3">
-        <v>9201900</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="3">
-        <v>8193900</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" s="3">
-        <v>7087200</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="D35" s="3">
+        <v>7282700</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3">
+        <v>9228200</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3">
+        <v>8217300</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3">
+        <v>7107500</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3">
         <v>7314400</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>5607400</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3">
         <v>4169100</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>569500</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>4556400</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>3844500</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>3962700</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>3298400</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="3">
         <v>3633000</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD35" s="3">
         <v>2386500</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF35" s="3">
         <v>2664500</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3317,8 +3401,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,28 +3436,29 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6667300</v>
+        <v>8458900</v>
       </c>
       <c r="E41" s="3">
-        <v>7920500</v>
+        <v>6686400</v>
       </c>
       <c r="F41" s="3">
-        <v>8570400</v>
+        <v>7943100</v>
       </c>
       <c r="G41" s="3">
-        <v>8702800</v>
+        <v>8594900</v>
       </c>
       <c r="H41" s="3">
-        <v>7844600</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>5</v>
+        <v>8727700</v>
+      </c>
+      <c r="I41" s="3">
+        <v>7867000</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>5</v>
@@ -3401,70 +3487,73 @@
       <c r="R41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T41" s="3">
         <v>6622700</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V41" s="3">
         <v>4704400</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W41" s="3">
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3">
         <v>5453200</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z41" s="3">
         <v>4635800</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3">
         <v>4194000</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" s="3">
         <v>9479700</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF41" s="3">
         <v>4160000</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4582000</v>
+        <v>3797500</v>
       </c>
       <c r="E42" s="3">
-        <v>3853900</v>
+        <v>4595000</v>
       </c>
       <c r="F42" s="3">
-        <v>2710300</v>
+        <v>3864900</v>
       </c>
       <c r="G42" s="3">
-        <v>2760200</v>
+        <v>2718100</v>
       </c>
       <c r="H42" s="3">
-        <v>1593900</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>5</v>
+        <v>2768100</v>
+      </c>
+      <c r="I42" s="3">
+        <v>1598400</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>5</v>
@@ -3493,70 +3582,73 @@
       <c r="R42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S42" s="3">
+      <c r="S42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T42" s="3">
         <v>855700</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U42" s="3">
+      <c r="U42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V42" s="3">
         <v>927000</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W42" s="3">
+      <c r="W42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X42" s="3">
         <v>787800</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y42" s="3">
+      <c r="Y42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z42" s="3">
         <v>799300</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB42" s="3">
         <v>577800</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC42" s="3">
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="3">
         <v>572200</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="3">
         <v>439000</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>7692700</v>
+        <v>8643900</v>
       </c>
       <c r="E43" s="3">
-        <v>7714400</v>
+        <v>7714600</v>
       </c>
       <c r="F43" s="3">
-        <v>7203300</v>
+        <v>7736400</v>
       </c>
       <c r="G43" s="3">
-        <v>6631500</v>
+        <v>7223900</v>
       </c>
       <c r="H43" s="3">
-        <v>5237300</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
+        <v>6650500</v>
+      </c>
+      <c r="I43" s="3">
+        <v>5252300</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
@@ -3585,70 +3677,73 @@
       <c r="R43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S43" s="3">
+      <c r="S43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T43" s="3">
         <v>6420800</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V43" s="3">
         <v>5759700</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W43" s="3">
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="3">
         <v>5939300</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z43" s="3">
         <v>4967400</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3">
         <v>5413600</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
         <v>4061600</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF43" s="3">
         <v>4816100</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>24562200</v>
+        <v>24974100</v>
       </c>
       <c r="E44" s="3">
-        <v>22046100</v>
+        <v>24632400</v>
       </c>
       <c r="F44" s="3">
-        <v>20528200</v>
+        <v>22109100</v>
       </c>
       <c r="G44" s="3">
-        <v>17955700</v>
+        <v>20586900</v>
       </c>
       <c r="H44" s="3">
-        <v>17177700</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
+        <v>18007000</v>
+      </c>
+      <c r="I44" s="3">
+        <v>17226800</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
@@ -3677,70 +3772,73 @@
       <c r="R44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S44" s="3">
+      <c r="S44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T44" s="3">
         <v>16013400</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U44" s="3">
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V44" s="3">
         <v>15953200</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W44" s="3">
+      <c r="W44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X44" s="3">
         <v>14768500</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="3">
         <v>13047500</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="3">
         <v>12216200</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD44" s="3">
         <v>12190400</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF44" s="3">
         <v>12379000</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2068000</v>
+        <v>1686600</v>
       </c>
       <c r="E45" s="3">
-        <v>1583000</v>
+        <v>2073900</v>
       </c>
       <c r="F45" s="3">
-        <v>1448500</v>
+        <v>1587500</v>
       </c>
       <c r="G45" s="3">
-        <v>1166400</v>
+        <v>1452600</v>
       </c>
       <c r="H45" s="3">
-        <v>1168500</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
+        <v>1169700</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1171900</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
@@ -3769,70 +3867,73 @@
       <c r="R45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T45" s="3">
         <v>1035500</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V45" s="3">
         <v>1014100</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W45" s="3">
+      <c r="W45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X45" s="3">
         <v>909700</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z45" s="3">
         <v>888300</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB45" s="3">
         <v>1228600</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD45" s="3">
         <v>1173600</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF45" s="3">
         <v>975400</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>45572200</v>
+        <v>47560900</v>
       </c>
       <c r="E46" s="3">
-        <v>43117900</v>
+        <v>45702400</v>
       </c>
       <c r="F46" s="3">
-        <v>40460700</v>
+        <v>43241100</v>
       </c>
       <c r="G46" s="3">
-        <v>37216600</v>
+        <v>40576300</v>
       </c>
       <c r="H46" s="3">
-        <v>33022000</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>5</v>
+        <v>37322900</v>
+      </c>
+      <c r="I46" s="3">
+        <v>33116300</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>5</v>
@@ -3861,70 +3962,73 @@
       <c r="R46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T46" s="3">
         <v>30948000</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V46" s="3">
         <v>28358300</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W46" s="3">
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X46" s="3">
         <v>27858500</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z46" s="3">
         <v>24338300</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB46" s="3">
         <v>23630200</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AC46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD46" s="3">
         <v>27477500</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF46" s="3">
         <v>22769600</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3627200</v>
+        <v>3453600</v>
       </c>
       <c r="E47" s="3">
-        <v>3442700</v>
+        <v>3637500</v>
       </c>
       <c r="F47" s="3">
-        <v>3720500</v>
+        <v>3452500</v>
       </c>
       <c r="G47" s="3">
-        <v>3626100</v>
+        <v>3731100</v>
       </c>
       <c r="H47" s="3">
-        <v>3020600</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
+        <v>3636400</v>
+      </c>
+      <c r="I47" s="3">
+        <v>3029300</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
@@ -3953,70 +4057,73 @@
       <c r="R47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T47" s="3">
         <v>3162500</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>2750400</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3">
         <v>2862600</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
         <v>2390300</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3">
         <v>2257400</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
         <v>2228300</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF47" s="3">
         <v>2461500</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>42669800</v>
+        <v>46446600</v>
       </c>
       <c r="E48" s="3">
-        <v>40564900</v>
+        <v>42791700</v>
       </c>
       <c r="F48" s="3">
-        <v>38425300</v>
+        <v>40680800</v>
       </c>
       <c r="G48" s="3">
-        <v>36446200</v>
+        <v>38535100</v>
       </c>
       <c r="H48" s="3">
-        <v>71404900</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
+        <v>36550400</v>
+      </c>
+      <c r="I48" s="3">
+        <v>71608900</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
@@ -4045,70 +4152,73 @@
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3">
         <v>35699400</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>32928600</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>17876000</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>15549900</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>30370000</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>27241900</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>14248900</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>55018200</v>
+        <v>54333200</v>
       </c>
       <c r="E49" s="3">
-        <v>54789200</v>
+        <v>55175400</v>
       </c>
       <c r="F49" s="3">
-        <v>55619300</v>
+        <v>54945800</v>
       </c>
       <c r="G49" s="3">
-        <v>55076800</v>
+        <v>55778200</v>
       </c>
       <c r="H49" s="3">
-        <v>105022600</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
+        <v>55234100</v>
+      </c>
+      <c r="I49" s="3">
+        <v>105322600</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
@@ -4137,50 +4247,53 @@
       <c r="R49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S49" s="3">
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T49" s="3">
         <v>39234300</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U49" s="3">
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V49" s="3">
         <v>39610600</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W49" s="3">
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="3">
         <v>36647400</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z49" s="3">
         <v>34095100</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3">
         <v>68466100</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD49" s="3">
         <v>56139900</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF49" s="3">
         <v>27861600</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4271,8 +4384,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4363,28 +4479,31 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4334600</v>
+        <v>4559100</v>
       </c>
       <c r="E52" s="3">
-        <v>4176200</v>
+        <v>4347000</v>
       </c>
       <c r="F52" s="3">
-        <v>4244500</v>
+        <v>4188100</v>
       </c>
       <c r="G52" s="3">
-        <v>3596800</v>
+        <v>4256600</v>
       </c>
       <c r="H52" s="3">
-        <v>3295100</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
+        <v>3607100</v>
+      </c>
+      <c r="I52" s="3">
+        <v>3304600</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
@@ -4413,50 +4532,53 @@
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T52" s="3">
         <v>3619000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="3">
         <v>3315100</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>2645000</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>2396900</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>2273200</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>2462800</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>2643400</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4547,28 +4669,31 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>151221900</v>
+        <v>156353400</v>
       </c>
       <c r="E54" s="3">
-        <v>146090900</v>
+        <v>151653900</v>
       </c>
       <c r="F54" s="3">
-        <v>142470300</v>
+        <v>146508300</v>
       </c>
       <c r="G54" s="3">
-        <v>135962400</v>
+        <v>142877300</v>
       </c>
       <c r="H54" s="3">
-        <v>128599600</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>5</v>
+        <v>136350900</v>
+      </c>
+      <c r="I54" s="3">
+        <v>128967100</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>5</v>
@@ -4597,50 +4722,53 @@
       <c r="R54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T54" s="3">
         <v>112663200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V54" s="3">
         <v>106963000</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W54" s="3">
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X54" s="3">
         <v>87889500</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="3">
         <v>78770500</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="3">
         <v>78264400</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD54" s="3">
         <v>73859500</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF54" s="3">
         <v>69984900</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +4801,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4707,28 +4836,29 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8923000</v>
+        <v>9846200</v>
       </c>
       <c r="E57" s="3">
-        <v>9535000</v>
+        <v>8948500</v>
       </c>
       <c r="F57" s="3">
-        <v>8212400</v>
+        <v>9562200</v>
       </c>
       <c r="G57" s="3">
-        <v>7688300</v>
+        <v>8235800</v>
       </c>
       <c r="H57" s="3">
-        <v>6142200</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
+        <v>7710300</v>
+      </c>
+      <c r="I57" s="3">
+        <v>6159700</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
@@ -4757,70 +4887,73 @@
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T57" s="3">
         <v>6787300</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>6073800</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>6285900</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>5059600</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>5092700</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>4320800</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3">
         <v>4911200</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>17877500</v>
+        <v>14632800</v>
       </c>
       <c r="E58" s="3">
-        <v>12945100</v>
+        <v>17928600</v>
       </c>
       <c r="F58" s="3">
-        <v>14804800</v>
+        <v>12982100</v>
       </c>
       <c r="G58" s="3">
-        <v>11285100</v>
+        <v>14847100</v>
       </c>
       <c r="H58" s="3">
-        <v>15689100</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>5</v>
+        <v>11317300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>15733900</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>5</v>
@@ -4849,70 +4982,73 @@
       <c r="R58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T58" s="3">
         <v>11395100</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="3">
         <v>11668700</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3">
         <v>5924000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>6213600</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>5487700</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>5463000</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="3">
         <v>4013300</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10404100</v>
+        <v>11586100</v>
       </c>
       <c r="E59" s="3">
-        <v>11744000</v>
+        <v>10433800</v>
       </c>
       <c r="F59" s="3">
-        <v>11631200</v>
+        <v>11777600</v>
       </c>
       <c r="G59" s="3">
-        <v>11394700</v>
+        <v>11664400</v>
       </c>
       <c r="H59" s="3">
-        <v>8461900</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
+        <v>11427200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>8486100</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
@@ -4941,70 +5077,73 @@
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="3">
         <v>8227900</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3">
         <v>7018400</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>7701900</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>6037900</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3">
         <v>6679200</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>5213900</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF59" s="3">
         <v>6112000</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>37204700</v>
+        <v>36065100</v>
       </c>
       <c r="E60" s="3">
-        <v>34224200</v>
+        <v>37310900</v>
       </c>
       <c r="F60" s="3">
-        <v>34648400</v>
+        <v>34321900</v>
       </c>
       <c r="G60" s="3">
-        <v>30368100</v>
+        <v>34747400</v>
       </c>
       <c r="H60" s="3">
-        <v>30293200</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>5</v>
+        <v>30454800</v>
+      </c>
+      <c r="I60" s="3">
+        <v>30379800</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>5</v>
@@ -5033,70 +5172,73 @@
       <c r="R60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S60" s="3">
+      <c r="S60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T60" s="3">
         <v>26410300</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V60" s="3">
         <v>24760900</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W60" s="3">
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X60" s="3">
         <v>19911800</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z60" s="3">
         <v>17311100</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB60" s="3">
         <v>16817500</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AC60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD60" s="3">
         <v>14997600</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF60" s="3">
         <v>15036500</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>23676900</v>
+        <v>27242800</v>
       </c>
       <c r="E61" s="3">
-        <v>25124300</v>
+        <v>23744500</v>
       </c>
       <c r="F61" s="3">
-        <v>25098200</v>
+        <v>25196000</v>
       </c>
       <c r="G61" s="3">
-        <v>26096400</v>
+        <v>25169900</v>
       </c>
       <c r="H61" s="3">
-        <v>26197300</v>
+        <v>26171000</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>26272200</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -5126,69 +5268,72 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>18064500</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>18501200</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>7103300</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>7347800</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>7905500</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>9213800</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>4615400</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>25838200</v>
+        <v>24820600</v>
       </c>
       <c r="E62" s="3">
-        <v>25327200</v>
+        <v>25912000</v>
       </c>
       <c r="F62" s="3">
-        <v>25530100</v>
+        <v>25399500</v>
       </c>
       <c r="G62" s="3">
-        <v>26431700</v>
+        <v>25603000</v>
       </c>
       <c r="H62" s="3">
-        <v>25862100</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
+        <v>26507200</v>
+      </c>
+      <c r="I62" s="3">
+        <v>25936000</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
@@ -5217,50 +5362,53 @@
       <c r="R62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T62" s="3">
         <v>23400700</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="3">
         <v>22068100</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>20706700</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3">
         <v>19544400</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3">
         <v>19458700</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>17915900</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="3">
         <v>17580200</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5351,8 +5499,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5443,8 +5594,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5535,28 +5689,31 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>88598900</v>
+        <v>89960800</v>
       </c>
       <c r="E66" s="3">
-        <v>86295500</v>
+        <v>88852100</v>
       </c>
       <c r="F66" s="3">
-        <v>87402200</v>
+        <v>86542000</v>
       </c>
       <c r="G66" s="3">
-        <v>84838300</v>
+        <v>87651900</v>
       </c>
       <c r="H66" s="3">
-        <v>83904100</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>5</v>
+        <v>85080700</v>
+      </c>
+      <c r="I66" s="3">
+        <v>84143900</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
@@ -5585,50 +5742,53 @@
       <c r="R66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T66" s="3">
         <v>69952400</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V66" s="3">
         <v>67344200</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W66" s="3">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3">
         <v>49690100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3">
         <v>45841500</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3">
         <v>45761500</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3">
         <v>43746400</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF66" s="3">
         <v>39004500</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5661,8 +5821,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5753,8 +5914,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5845,8 +6009,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5937,8 +6104,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6029,28 +6199,31 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>60520200</v>
+        <v>64603800</v>
       </c>
       <c r="E72" s="3">
-        <v>55434800</v>
+        <v>60693100</v>
       </c>
       <c r="F72" s="3">
-        <v>50161700</v>
+        <v>55593200</v>
       </c>
       <c r="G72" s="3">
-        <v>47087900</v>
+        <v>50305000</v>
       </c>
       <c r="H72" s="3">
-        <v>41705200</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
+        <v>47222500</v>
+      </c>
+      <c r="I72" s="3">
+        <v>41824400</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
@@ -6079,50 +6252,53 @@
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>38341200</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>35396700</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>34086400</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>29060800</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>28350400</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>25598200</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3">
         <v>25760400</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6213,8 +6389,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6305,8 +6484,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6397,28 +6579,31 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>62622900</v>
+        <v>66392600</v>
       </c>
       <c r="E76" s="3">
-        <v>59795400</v>
+        <v>62801900</v>
       </c>
       <c r="F76" s="3">
-        <v>55068100</v>
+        <v>59966300</v>
       </c>
       <c r="G76" s="3">
-        <v>51124100</v>
+        <v>55225400</v>
       </c>
       <c r="H76" s="3">
-        <v>44695500</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>5</v>
+        <v>51270200</v>
+      </c>
+      <c r="I76" s="3">
+        <v>44823200</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
@@ -6447,50 +6632,53 @@
       <c r="R76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S76" s="3">
+      <c r="S76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T76" s="3">
         <v>42710900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V76" s="3">
         <v>39618800</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W76" s="3">
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="3">
         <v>38199400</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z76" s="3">
         <v>32929000</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="3">
         <v>32502900</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC76" s="3">
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD76" s="3">
         <v>30113100</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF76" s="3">
         <v>30980400</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6581,197 +6769,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E81" s="3">
-        <v>9201900</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G81" s="3">
-        <v>8193900</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I81" s="3">
-        <v>7087200</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="D81" s="3">
+        <v>7282700</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3">
+        <v>9228200</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3">
+        <v>8217300</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3">
+        <v>7107500</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3">
         <v>7314400</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>5607400</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3">
         <v>4169100</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>569500</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>4556400</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>3844500</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>3962700</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>3298400</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="3">
         <v>3633000</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD81" s="3">
         <v>2386500</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF81" s="3">
         <v>2664500</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6804,100 +7001,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
         <v>6320300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>6034300</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>3203400</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>2781000</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>1462100</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1170500</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>1532600</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>1133200</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF83" s="3">
         <v>1526000</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6988,8 +7189,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7080,8 +7284,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7172,8 +7379,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7264,8 +7474,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7356,100 +7569,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
         <v>20216300</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
         <v>10868700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>8707700</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>4927900</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>6303700</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>3470800</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>5345200</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>2542400</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>5407700</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7482,100 +7701,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4204000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3603000</v>
       </c>
-      <c r="E91" s="3">
-        <v>-3313000</v>
-      </c>
       <c r="F91" s="3">
-        <v>-1769000</v>
+        <v>-3314000</v>
       </c>
       <c r="G91" s="3">
+        <v>-1768000</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1523000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1141000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1197000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1978800</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T91" s="3">
         <v>-2034800</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V91" s="3">
         <v>-1314000</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-1961200</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-1038700</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-1257800</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-861700</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-1928600</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7666,8 +7889,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,100 +7984,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
         <v>-17322800</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-2931400</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-2896300</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-3985600</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-2602400</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-1360400</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-8053600</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-1603300</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-1367500</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7884,8 +8116,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7911,11 +8144,11 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-4510900</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -7923,11 +8156,11 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-2427700</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -7935,49 +8168,52 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-1367000</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-2837500</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-1190000</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1876500</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-902100</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1465300</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-826400</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8068,8 +8304,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8160,8 +8399,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8252,280 +8494,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>-16430600</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>7383800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>-3917800</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>-1621100</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>-3320400</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-1664600</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-2373000</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>4794300</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-3366500</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
         <v>539900</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>-1049300</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>28000</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>17600</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>45000</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>31800</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-30300</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-97600</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
         <v>-12997300</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
         <v>14271800</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>1921600</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>-661100</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>425800</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>477600</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-5270000</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>5585300</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>672600</v>
       </c>
-      <c r="AF102" s="3" t="s">
+      <c r="AG102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="92">
   <si>
     <t>LVMUY</t>
   </si>
@@ -656,427 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>47781700</v>
+        <v>22364000</v>
       </c>
       <c r="E8" s="3">
-        <v>21722800</v>
+        <v>47456800</v>
       </c>
       <c r="F8" s="3">
-        <v>45961300</v>
+        <v>21575100</v>
       </c>
       <c r="G8" s="3">
-        <v>22888200</v>
+        <v>45648800</v>
       </c>
       <c r="H8" s="3">
-        <v>46195300</v>
+        <v>22732500</v>
       </c>
       <c r="I8" s="3">
-        <v>21495400</v>
+        <v>45881100</v>
       </c>
       <c r="J8" s="3">
+        <v>21349200</v>
+      </c>
+      <c r="K8" s="3">
         <v>39964800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19533300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>38539800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16704900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>30327600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14249300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>26189700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12408100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>20065100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11963900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>33373900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16312000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>29506500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>14998000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>29662400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>12603400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>23881500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>12178100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>25718300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11647400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>22118900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11601900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>23959800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10726300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>15182300</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3">
-        <v>14061500</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3">
-        <v>14765500</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
+        <v>15079000</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3">
+        <v>13965900</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="3">
+        <v>14665100</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="3">
         <v>12423900</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3">
         <v>12191800</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="3">
         <v>9635200</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
         <v>8845900</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3">
         <v>7638600</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3">
         <v>11295900</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W9" s="3">
         <v>9937100</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3">
         <v>10048700</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3">
         <v>7828700</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB9" s="3">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC9" s="3">
         <v>8866000</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD9" s="3">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3">
         <v>7720400</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF9" s="3">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3">
         <v>8359900</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>32599500</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3">
-        <v>31899800</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3">
-        <v>31429800</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>32377800</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3">
+        <v>31682900</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="3">
+        <v>31216000</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3">
         <v>27540900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="3">
         <v>26348000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3">
         <v>20692400</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3">
         <v>17343800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3">
         <v>12426600</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="3">
         <v>22078100</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W10" s="3">
         <v>19569400</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3">
         <v>19613700</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3">
         <v>16052800</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="3">
         <v>16852300</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD10" s="3">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3">
         <v>14398500</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF10" s="3">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="3">
         <v>15599900</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1110,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1205,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1300,103 +1318,109 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>226300</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
-        <v>8700</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
-        <v>189300</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>224800</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
+        <v>8600</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
+        <v>188000</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>117500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>94300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
         <v>32800</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>150600</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>136400</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>101600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>48200</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
         <v>62700</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="3">
         <v>80200</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="3">
         <v>150300</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE14" s="3">
         <v>111100</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="3">
         <v>159600</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1481,8 +1505,8 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>5</v>
+      <c r="AE15" s="3">
+        <v>0</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>5</v>
@@ -1490,8 +1514,11 @@
       <c r="AG15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1522,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>35817000</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="3">
-        <v>33378600</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H17" s="3">
-        <v>34363300</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3">
+        <v>35573400</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3">
+        <v>33151600</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3">
+        <v>34129600</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3">
         <v>28945600</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3">
         <v>28179000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" s="3">
         <v>22300500</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3">
         <v>19751500</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3">
         <v>18410200</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U17" s="3">
         <v>26332100</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W17" s="3">
         <v>23341000</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="3">
         <v>23394200</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA17" s="3">
         <v>18854900</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB17" s="3">
+      <c r="AB17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC17" s="3">
         <v>20593000</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AD17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="3">
         <v>18141500</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="3">
         <v>19282200</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>11964700</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="3">
-        <v>12582800</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H18" s="3">
-        <v>11832000</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3">
+        <v>11883400</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3">
+        <v>12497200</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3">
+        <v>11751500</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>11019200</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3">
         <v>10360700</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" s="3">
         <v>8027000</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="3">
         <v>6438200</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3">
         <v>1654900</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" s="3">
         <v>7041800</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="3">
         <v>6165500</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3">
         <v>6268200</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA18" s="3">
         <v>5026600</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC18" s="3">
         <v>5125300</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="3">
         <v>3977500</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG18" s="3">
         <v>4677600</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1747,123 +1781,127 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-907500</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3">
-        <v>948800</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="3">
-        <v>175200</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-901300</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3">
+        <v>942400</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3">
+        <v>174000</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-725800</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>181000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O20" s="3">
         <v>153400</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>4000</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3">
         <v>-268400</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="3">
         <v>-151800</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="3">
         <v>20000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-332400</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA20" s="3">
         <v>56000</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC20" s="3">
         <v>57200</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE20" s="3">
         <v>66200</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-248800</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
+      <c r="E21" s="3">
+        <v>18738300</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
+      <c r="G21" s="3">
+        <v>16767100</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
+      <c r="I21" s="3">
+        <v>18654000</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>5</v>
@@ -1871,359 +1909,371 @@
       <c r="K21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="3">
         <v>16862100</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>12476500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3">
         <v>10093400</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="3">
         <v>8966500</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3">
         <v>7397900</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="3">
         <v>6253100</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3">
         <v>6715100</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="3">
         <v>5176900</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="3">
         <v>5954700</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>618000</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="3">
-        <v>440700</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" s="3">
-        <v>273100</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3">
+        <v>613800</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3">
+        <v>437700</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3">
+        <v>271300</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3">
         <v>142500</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3">
         <v>110600</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="3">
         <v>140700</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3">
         <v>149600</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="3">
         <v>235600</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" s="3">
         <v>261500</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3">
         <v>261200</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3">
         <v>100500</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3">
         <v>80200</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="3">
         <v>102100</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE22" s="3">
         <v>87500</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG22" s="3">
         <v>63400</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>10439200</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="3">
-        <v>13090900</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H23" s="3">
-        <v>11734100</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3">
+        <v>10368200</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3">
+        <v>13001900</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3">
+        <v>11654300</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
         <v>10150900</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="3">
         <v>10431200</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O23" s="3">
         <v>8039700</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="3">
         <v>6292600</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3">
         <v>1150900</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" s="3">
         <v>6628600</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W23" s="3">
         <v>5924400</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="3">
         <v>5835200</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="3">
         <v>5002500</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AB23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC23" s="3">
         <v>5080400</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AD23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE23" s="3">
         <v>3956100</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF23" s="3">
+      <c r="AF23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG23" s="3">
         <v>4365400</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>2768100</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="3">
-        <v>3404700</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H24" s="3">
-        <v>3239300</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2749300</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3">
+        <v>3381500</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3">
+        <v>3217200</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>2595100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3">
         <v>2710300</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="3">
         <v>2128700</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="3">
         <v>1893100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3">
         <v>557500</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U24" s="3">
         <v>1752300</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W24" s="3">
         <v>1683400</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y24" s="3">
         <v>1460900</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="Z24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA24" s="3">
         <v>1387900</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AB24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC24" s="3">
         <v>1154500</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AD24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE24" s="3">
         <v>1329600</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AF24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG24" s="3">
         <v>1430900</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2317,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>7671100</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="3">
-        <v>9686300</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H26" s="3">
-        <v>8494800</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3">
+        <v>7618900</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3">
+        <v>9620400</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3">
+        <v>8437000</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
         <v>7555800</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M26" s="3">
         <v>7721000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="3">
         <v>5911000</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3">
         <v>4399500</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3">
         <v>593500</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U26" s="3">
         <v>4876300</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W26" s="3">
         <v>4240900</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y26" s="3">
         <v>4374400</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA26" s="3">
         <v>3614600</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC26" s="3">
         <v>3925800</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AD26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE26" s="3">
         <v>2626600</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF26" s="3">
+      <c r="AF26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG26" s="3">
         <v>2934500</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>7282700</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="3">
-        <v>9228200</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H27" s="3">
-        <v>8217300</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3">
+        <v>7233100</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3">
+        <v>9165400</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3">
+        <v>8161400</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
         <v>7107500</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="3">
         <v>7314400</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="3">
         <v>5607400</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3">
         <v>4169100</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3">
         <v>569500</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" s="3">
         <v>4556400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W27" s="3">
         <v>3844500</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y27" s="3">
         <v>3962700</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA27" s="3">
         <v>3298400</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC27" s="3">
         <v>3633000</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AD27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE27" s="3">
         <v>2386500</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AF27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG27" s="3">
         <v>2664500</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2602,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2697,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2792,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2887,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>907500</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-948800</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-175200</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
+        <v>901300</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-942400</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>725800</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>-181000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O32" s="3">
         <v>-153400</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3">
         <v>268400</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U32" s="3">
         <v>151800</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W32" s="3">
         <v>-20000</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y32" s="3">
         <v>332400</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-57200</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-66200</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG32" s="3">
         <v>248800</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>7282700</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="3">
-        <v>9228200</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H33" s="3">
-        <v>8217300</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3">
+        <v>7233100</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3">
+        <v>9165400</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3">
+        <v>8161400</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
         <v>7107500</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3">
         <v>7314400</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O33" s="3">
         <v>5607400</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="3">
         <v>4169100</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3">
         <v>569500</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3">
         <v>4556400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W33" s="3">
         <v>3844500</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="3">
         <v>3962700</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA33" s="3">
         <v>3298400</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC33" s="3">
         <v>3633000</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AD33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE33" s="3">
         <v>2386500</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AF33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG33" s="3">
         <v>2664500</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3172,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>7282700</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" s="3">
-        <v>9228200</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H35" s="3">
-        <v>8217300</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3">
+        <v>7233100</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3">
+        <v>9165400</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="3">
+        <v>8161400</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
         <v>7107500</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M35" s="3">
         <v>7314400</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O35" s="3">
         <v>5607400</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3">
         <v>4169100</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3">
         <v>569500</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U35" s="3">
         <v>4556400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W35" s="3">
         <v>3844500</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y35" s="3">
         <v>3962700</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA35" s="3">
         <v>3298400</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC35" s="3">
         <v>3633000</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD35" s="3">
+      <c r="AD35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE35" s="3">
         <v>2386500</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AF35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG35" s="3">
         <v>2664500</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3402,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3437,28 +3524,29 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8458900</v>
+        <v>8401400</v>
       </c>
       <c r="E41" s="3">
-        <v>6686400</v>
+        <v>6640900</v>
       </c>
       <c r="F41" s="3">
-        <v>7943100</v>
+        <v>7889100</v>
       </c>
       <c r="G41" s="3">
-        <v>8594900</v>
+        <v>8536400</v>
       </c>
       <c r="H41" s="3">
-        <v>8727700</v>
-      </c>
-      <c r="I41" s="3">
-        <v>7867000</v>
+        <v>8668300</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>5</v>
@@ -3490,70 +3578,73 @@
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T41" s="3">
+      <c r="T41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U41" s="3">
         <v>6622700</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V41" s="3">
+      <c r="V41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W41" s="3">
         <v>4704400</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X41" s="3">
+      <c r="X41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y41" s="3">
         <v>5453200</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z41" s="3">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA41" s="3">
         <v>4635800</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3">
         <v>4194000</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD41" s="3">
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE41" s="3">
         <v>9479700</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG41" s="3">
         <v>4160000</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3797500</v>
+        <v>3771600</v>
       </c>
       <c r="E42" s="3">
-        <v>4595000</v>
+        <v>4563800</v>
       </c>
       <c r="F42" s="3">
-        <v>3864900</v>
+        <v>3838600</v>
       </c>
       <c r="G42" s="3">
-        <v>2718100</v>
+        <v>2699600</v>
       </c>
       <c r="H42" s="3">
-        <v>2768100</v>
-      </c>
-      <c r="I42" s="3">
-        <v>1598400</v>
+        <v>2749300</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>5</v>
@@ -3585,70 +3676,73 @@
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T42" s="3">
+      <c r="T42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U42" s="3">
         <v>855700</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V42" s="3">
+      <c r="V42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W42" s="3">
         <v>927000</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X42" s="3">
+      <c r="X42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y42" s="3">
         <v>787800</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z42" s="3">
+      <c r="Z42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA42" s="3">
         <v>799300</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB42" s="3">
+      <c r="AB42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC42" s="3">
         <v>577800</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD42" s="3">
+      <c r="AD42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE42" s="3">
         <v>572200</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF42" s="3">
+      <c r="AF42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG42" s="3">
         <v>439000</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8643900</v>
+        <v>8585100</v>
       </c>
       <c r="E43" s="3">
-        <v>7714600</v>
+        <v>7662200</v>
       </c>
       <c r="F43" s="3">
-        <v>7736400</v>
+        <v>7683800</v>
       </c>
       <c r="G43" s="3">
-        <v>7223900</v>
+        <v>7174800</v>
       </c>
       <c r="H43" s="3">
-        <v>6650500</v>
-      </c>
-      <c r="I43" s="3">
-        <v>5252300</v>
+        <v>6605200</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
@@ -3680,70 +3774,73 @@
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T43" s="3">
+      <c r="T43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U43" s="3">
         <v>6420800</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V43" s="3">
+      <c r="V43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W43" s="3">
         <v>5759700</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X43" s="3">
+      <c r="X43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y43" s="3">
         <v>5939300</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z43" s="3">
+      <c r="Z43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA43" s="3">
         <v>4967400</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3">
         <v>5413600</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD43" s="3">
+      <c r="AD43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="3">
         <v>4061600</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF43" s="3">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG43" s="3">
         <v>4816100</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>24974100</v>
+        <v>24804200</v>
       </c>
       <c r="E44" s="3">
-        <v>24632400</v>
+        <v>24464900</v>
       </c>
       <c r="F44" s="3">
-        <v>22109100</v>
+        <v>21958700</v>
       </c>
       <c r="G44" s="3">
-        <v>20586900</v>
+        <v>20446800</v>
       </c>
       <c r="H44" s="3">
-        <v>18007000</v>
-      </c>
-      <c r="I44" s="3">
-        <v>17226800</v>
+        <v>17884500</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
@@ -3775,70 +3872,73 @@
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T44" s="3">
+      <c r="T44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U44" s="3">
         <v>16013400</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V44" s="3">
+      <c r="V44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W44" s="3">
         <v>15953200</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X44" s="3">
+      <c r="X44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y44" s="3">
         <v>14768500</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z44" s="3">
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="3">
         <v>13047500</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB44" s="3">
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3">
         <v>12216200</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD44" s="3">
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE44" s="3">
         <v>12190400</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF44" s="3">
+      <c r="AF44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG44" s="3">
         <v>12379000</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1686600</v>
+        <v>1675100</v>
       </c>
       <c r="E45" s="3">
-        <v>2073900</v>
+        <v>2059800</v>
       </c>
       <c r="F45" s="3">
-        <v>1587500</v>
+        <v>1576700</v>
       </c>
       <c r="G45" s="3">
-        <v>1452600</v>
+        <v>1442700</v>
       </c>
       <c r="H45" s="3">
-        <v>1169700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1171900</v>
+        <v>1161800</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
@@ -3870,70 +3970,73 @@
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U45" s="3">
         <v>1035500</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W45" s="3">
         <v>1014100</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y45" s="3">
         <v>909700</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA45" s="3">
         <v>888300</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC45" s="3">
         <v>1228600</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE45" s="3">
         <v>1173600</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG45" s="3">
         <v>975400</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>47560900</v>
+        <v>47237400</v>
       </c>
       <c r="E46" s="3">
-        <v>45702400</v>
+        <v>45391600</v>
       </c>
       <c r="F46" s="3">
-        <v>43241100</v>
+        <v>42947000</v>
       </c>
       <c r="G46" s="3">
-        <v>40576300</v>
+        <v>40300400</v>
       </c>
       <c r="H46" s="3">
-        <v>37322900</v>
-      </c>
-      <c r="I46" s="3">
-        <v>33116300</v>
+        <v>37069100</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>5</v>
@@ -3965,70 +4068,73 @@
       <c r="S46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U46" s="3">
         <v>30948000</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V46" s="3">
+      <c r="V46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W46" s="3">
         <v>28358300</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X46" s="3">
+      <c r="X46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y46" s="3">
         <v>27858500</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z46" s="3">
+      <c r="Z46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA46" s="3">
         <v>24338300</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB46" s="3">
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC46" s="3">
         <v>23630200</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD46" s="3">
+      <c r="AD46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE46" s="3">
         <v>27477500</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF46" s="3">
+      <c r="AF46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG46" s="3">
         <v>22769600</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3453600</v>
+        <v>3430100</v>
       </c>
       <c r="E47" s="3">
-        <v>3637500</v>
+        <v>3612800</v>
       </c>
       <c r="F47" s="3">
-        <v>3452500</v>
+        <v>3429100</v>
       </c>
       <c r="G47" s="3">
-        <v>3731100</v>
+        <v>3705700</v>
       </c>
       <c r="H47" s="3">
-        <v>3636400</v>
-      </c>
-      <c r="I47" s="3">
-        <v>3029300</v>
+        <v>3611700</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
@@ -4060,70 +4166,73 @@
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U47" s="3">
         <v>3162500</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W47" s="3">
         <v>2750400</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="X47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y47" s="3">
         <v>2862600</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="3">
         <v>2390300</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3">
         <v>2257400</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD47" s="3">
+      <c r="AD47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="3">
         <v>2228300</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF47" s="3">
+      <c r="AF47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG47" s="3">
         <v>2461500</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>46446600</v>
+        <v>46130800</v>
       </c>
       <c r="E48" s="3">
-        <v>42791700</v>
+        <v>42500700</v>
       </c>
       <c r="F48" s="3">
-        <v>40680800</v>
+        <v>40404100</v>
       </c>
       <c r="G48" s="3">
-        <v>38535100</v>
+        <v>38273000</v>
       </c>
       <c r="H48" s="3">
-        <v>36550400</v>
-      </c>
-      <c r="I48" s="3">
-        <v>71608900</v>
+        <v>36301800</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
@@ -4155,70 +4264,73 @@
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3">
         <v>35699400</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V48" s="3">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W48" s="3">
         <v>32928600</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3">
         <v>17876000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3">
         <v>15549900</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>30370000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>27241900</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
         <v>14248900</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>54333200</v>
+        <v>53963700</v>
       </c>
       <c r="E49" s="3">
-        <v>55175400</v>
+        <v>54800100</v>
       </c>
       <c r="F49" s="3">
-        <v>54945800</v>
+        <v>54572100</v>
       </c>
       <c r="G49" s="3">
-        <v>55778200</v>
+        <v>55398800</v>
       </c>
       <c r="H49" s="3">
-        <v>55234100</v>
-      </c>
-      <c r="I49" s="3">
-        <v>105322600</v>
+        <v>54858500</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
@@ -4250,50 +4362,53 @@
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T49" s="3">
+      <c r="T49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U49" s="3">
         <v>39234300</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V49" s="3">
+      <c r="V49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W49" s="3">
         <v>39610600</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X49" s="3">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y49" s="3">
         <v>36647400</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z49" s="3">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA49" s="3">
         <v>34095100</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3">
         <v>68466100</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD49" s="3">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE49" s="3">
         <v>56139900</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF49" s="3">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG49" s="3">
         <v>27861600</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4387,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4482,28 +4600,31 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4559100</v>
+        <v>4528100</v>
       </c>
       <c r="E52" s="3">
-        <v>4347000</v>
+        <v>4317400</v>
       </c>
       <c r="F52" s="3">
-        <v>4188100</v>
+        <v>4159600</v>
       </c>
       <c r="G52" s="3">
-        <v>4256600</v>
+        <v>4227700</v>
       </c>
       <c r="H52" s="3">
-        <v>3607100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>3304600</v>
+        <v>3582500</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
@@ -4535,50 +4656,53 @@
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U52" s="3">
         <v>3619000</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W52" s="3">
         <v>3315100</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y52" s="3">
         <v>2645000</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA52" s="3">
         <v>2396900</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>2273200</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
         <v>2462800</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
         <v>2643400</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4672,28 +4796,31 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>156353400</v>
+        <v>155290100</v>
       </c>
       <c r="E54" s="3">
-        <v>151653900</v>
+        <v>150622600</v>
       </c>
       <c r="F54" s="3">
-        <v>146508300</v>
+        <v>145511900</v>
       </c>
       <c r="G54" s="3">
-        <v>142877300</v>
+        <v>141905600</v>
       </c>
       <c r="H54" s="3">
-        <v>136350900</v>
-      </c>
-      <c r="I54" s="3">
-        <v>128967100</v>
+        <v>135423600</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>5</v>
@@ -4725,50 +4852,53 @@
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T54" s="3">
+      <c r="T54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U54" s="3">
         <v>112663200</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W54" s="3">
         <v>106963000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X54" s="3">
+      <c r="X54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y54" s="3">
         <v>87889500</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z54" s="3">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA54" s="3">
         <v>78770500</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3">
         <v>78264400</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD54" s="3">
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE54" s="3">
         <v>73859500</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG54" s="3">
         <v>69984900</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4802,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4837,28 +4968,29 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9846200</v>
+        <v>9779300</v>
       </c>
       <c r="E57" s="3">
-        <v>8948500</v>
+        <v>8887700</v>
       </c>
       <c r="F57" s="3">
-        <v>9562200</v>
+        <v>9497200</v>
       </c>
       <c r="G57" s="3">
-        <v>8235800</v>
+        <v>8179800</v>
       </c>
       <c r="H57" s="3">
-        <v>7710300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>6159700</v>
+        <v>7657800</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
@@ -4890,70 +5022,73 @@
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U57" s="3">
         <v>6787300</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W57" s="3">
         <v>6073800</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y57" s="3">
         <v>6285900</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="3">
         <v>5059600</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3">
         <v>5092700</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3">
         <v>4320800</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="3">
         <v>4911200</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>14632800</v>
+        <v>14533300</v>
       </c>
       <c r="E58" s="3">
-        <v>17928600</v>
+        <v>17806700</v>
       </c>
       <c r="F58" s="3">
-        <v>12982100</v>
+        <v>12893800</v>
       </c>
       <c r="G58" s="3">
-        <v>14847100</v>
+        <v>14746200</v>
       </c>
       <c r="H58" s="3">
-        <v>11317300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>15733900</v>
+        <v>11240400</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>5</v>
@@ -4985,70 +5120,73 @@
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U58" s="3">
         <v>11395100</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W58" s="3">
         <v>11668700</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y58" s="3">
         <v>5924000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA58" s="3">
         <v>6213600</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3">
         <v>5487700</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD58" s="3">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="3">
         <v>5463000</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG58" s="3">
         <v>4013300</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>11586100</v>
+        <v>11507300</v>
       </c>
       <c r="E59" s="3">
-        <v>10433800</v>
+        <v>10362800</v>
       </c>
       <c r="F59" s="3">
-        <v>11777600</v>
+        <v>11697500</v>
       </c>
       <c r="G59" s="3">
-        <v>11664400</v>
+        <v>11585100</v>
       </c>
       <c r="H59" s="3">
-        <v>11427200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>8486100</v>
+        <v>11349500</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
@@ -5080,70 +5218,73 @@
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U59" s="3">
         <v>8227900</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W59" s="3">
         <v>7018400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y59" s="3">
         <v>7701900</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA59" s="3">
         <v>6037900</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3">
         <v>6679200</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE59" s="3">
         <v>5213900</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG59" s="3">
         <v>6112000</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>36065100</v>
+        <v>35819800</v>
       </c>
       <c r="E60" s="3">
-        <v>37310900</v>
+        <v>37057200</v>
       </c>
       <c r="F60" s="3">
-        <v>34321900</v>
+        <v>34088500</v>
       </c>
       <c r="G60" s="3">
-        <v>34747400</v>
+        <v>34511100</v>
       </c>
       <c r="H60" s="3">
-        <v>30454800</v>
-      </c>
-      <c r="I60" s="3">
-        <v>30379800</v>
+        <v>30247700</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>5</v>
@@ -5175,70 +5316,73 @@
       <c r="S60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T60" s="3">
+      <c r="T60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U60" s="3">
         <v>26410300</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V60" s="3">
+      <c r="V60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W60" s="3">
         <v>24760900</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X60" s="3">
+      <c r="X60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y60" s="3">
         <v>19911800</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z60" s="3">
+      <c r="Z60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA60" s="3">
         <v>17311100</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB60" s="3">
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC60" s="3">
         <v>16817500</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD60" s="3">
+      <c r="AD60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE60" s="3">
         <v>14997600</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF60" s="3">
+      <c r="AF60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG60" s="3">
         <v>15036500</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>27242800</v>
+        <v>27057500</v>
       </c>
       <c r="E61" s="3">
-        <v>23744500</v>
+        <v>23583000</v>
       </c>
       <c r="F61" s="3">
-        <v>25196000</v>
+        <v>25024700</v>
       </c>
       <c r="G61" s="3">
-        <v>25169900</v>
+        <v>24998800</v>
       </c>
       <c r="H61" s="3">
-        <v>26171000</v>
+        <v>25993000</v>
       </c>
       <c r="I61" s="3">
-        <v>26272200</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -5271,69 +5415,72 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>18064500</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>18501200</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>7103300</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>7347800</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>7905500</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>9213800</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>4615400</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>24820600</v>
+        <v>24651800</v>
       </c>
       <c r="E62" s="3">
-        <v>25912000</v>
+        <v>25735800</v>
       </c>
       <c r="F62" s="3">
-        <v>25399500</v>
+        <v>25226800</v>
       </c>
       <c r="G62" s="3">
-        <v>25603000</v>
+        <v>25428900</v>
       </c>
       <c r="H62" s="3">
-        <v>26507200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>25936000</v>
+        <v>26326900</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
@@ -5365,50 +5512,53 @@
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U62" s="3">
         <v>23400700</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V62" s="3">
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W62" s="3">
         <v>22068100</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X62" s="3">
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y62" s="3">
         <v>20706700</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA62" s="3">
         <v>19544400</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC62" s="3">
         <v>19458700</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AD62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE62" s="3">
         <v>17915900</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG62" s="3">
         <v>17580200</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5502,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5597,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5692,28 +5848,31 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>89960800</v>
+        <v>89349000</v>
       </c>
       <c r="E66" s="3">
-        <v>88852100</v>
+        <v>88247800</v>
       </c>
       <c r="F66" s="3">
-        <v>86542000</v>
+        <v>85953500</v>
       </c>
       <c r="G66" s="3">
-        <v>87651900</v>
+        <v>87055800</v>
       </c>
       <c r="H66" s="3">
-        <v>85080700</v>
-      </c>
-      <c r="I66" s="3">
-        <v>84143900</v>
+        <v>84502100</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
@@ -5745,50 +5904,53 @@
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T66" s="3">
+      <c r="T66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U66" s="3">
         <v>69952400</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W66" s="3">
         <v>67344200</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X66" s="3">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y66" s="3">
         <v>49690100</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="3">
         <v>45841500</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
         <v>45761500</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD66" s="3">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="3">
         <v>43746400</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG66" s="3">
         <v>39004500</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5822,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5917,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6012,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6107,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6202,28 +6374,31 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>64603800</v>
+        <v>64164400</v>
       </c>
       <c r="E72" s="3">
-        <v>60693100</v>
+        <v>60280400</v>
       </c>
       <c r="F72" s="3">
-        <v>55593200</v>
+        <v>55215100</v>
       </c>
       <c r="G72" s="3">
-        <v>50305000</v>
+        <v>49962900</v>
       </c>
       <c r="H72" s="3">
-        <v>47222500</v>
-      </c>
-      <c r="I72" s="3">
-        <v>41824400</v>
+        <v>46901300</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
@@ -6255,50 +6430,53 @@
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U72" s="3">
         <v>38341200</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W72" s="3">
         <v>35396700</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y72" s="3">
         <v>34086400</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="3">
         <v>29060800</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>28350400</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="3">
         <v>25598200</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="3">
         <v>25760400</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6392,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6487,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6582,28 +6766,31 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>66392600</v>
+        <v>65941100</v>
       </c>
       <c r="E76" s="3">
-        <v>62801900</v>
+        <v>62374800</v>
       </c>
       <c r="F76" s="3">
-        <v>59966300</v>
+        <v>59558500</v>
       </c>
       <c r="G76" s="3">
-        <v>55225400</v>
+        <v>54849800</v>
       </c>
       <c r="H76" s="3">
-        <v>51270200</v>
-      </c>
-      <c r="I76" s="3">
-        <v>44823200</v>
+        <v>50921500</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
@@ -6635,50 +6822,53 @@
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T76" s="3">
+      <c r="T76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U76" s="3">
         <v>42710900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V76" s="3">
+      <c r="V76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W76" s="3">
         <v>39618800</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X76" s="3">
+      <c r="X76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y76" s="3">
         <v>38199400</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA76" s="3">
         <v>32929000</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3">
         <v>32502900</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD76" s="3">
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE76" s="3">
         <v>30113100</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF76" s="3">
+      <c r="AF76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG76" s="3">
         <v>30980400</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6772,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>7282700</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" s="3">
-        <v>9228200</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H81" s="3">
-        <v>8217300</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3">
+        <v>7233100</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3">
+        <v>9165400</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I81" s="3">
+        <v>8161400</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
         <v>7107500</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3">
         <v>7314400</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O81" s="3">
         <v>5607400</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="3">
         <v>4169100</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3">
         <v>569500</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U81" s="3">
         <v>4556400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W81" s="3">
         <v>3844500</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y81" s="3">
         <v>3962700</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA81" s="3">
         <v>3298400</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC81" s="3">
         <v>3633000</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD81" s="3">
+      <c r="AD81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE81" s="3">
         <v>2386500</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AF81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG81" s="3">
         <v>2664500</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7002,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
+        <v>7756200</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
+        <v>3327500</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3">
+        <v>6728400</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3">
         <v>6320300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>6034300</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3">
         <v>3203400</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W83" s="3">
         <v>2781000</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1462100</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA83" s="3">
         <v>1170500</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC83" s="3">
         <v>1532600</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE83" s="3">
         <v>1133200</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG83" s="3">
         <v>1526000</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7192,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7287,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7382,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7477,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7572,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
+        <v>19884900</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
+        <v>7294700</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
+        <v>19272100</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
         <v>20216300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
         <v>10868700</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3">
         <v>8707700</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W89" s="3">
         <v>4927900</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3">
         <v>6303700</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA89" s="3">
         <v>3470800</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC89" s="3">
         <v>5345200</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE89" s="3">
         <v>2542400</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG89" s="3">
         <v>5407700</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7702,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7726,79 +7948,82 @@
         <v>-1141000</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1197000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1978800</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U91" s="3">
         <v>-2034800</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W91" s="3">
         <v>-1314000</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-1961200</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-1038700</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-1257800</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-861700</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-1928600</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7892,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7987,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+        <v>-8980600</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
+        <v>-4425500</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
+        <v>-6397700</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
         <v>-17322800</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-2931400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3">
         <v>-2896300</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W94" s="3">
         <v>-3985600</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-2602400</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-1360400</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-8053600</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-1603300</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-1367500</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8117,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8126,19 +8361,19 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-7161800</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-4026700</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-6865700</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -8147,11 +8382,11 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-4510900</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -8159,11 +8394,11 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-2427700</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -8171,49 +8406,52 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-1367000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-2837500</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-1190000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-1876500</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-902100</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-1465300</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-826400</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8307,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8402,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8497,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
+        <v>-10155300</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
+        <v>-4335800</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
+        <v>-13708700</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
         <v>-16430600</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>7383800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3">
         <v>-3917800</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W100" s="3">
         <v>-1621100</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-3320400</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-1664600</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-2373000</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE100" s="3">
         <v>4794300</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-3366500</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
+        <v>-295000</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
+        <v>-252900</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
+        <v>59400</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
         <v>539900</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-1049300</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U101" s="3">
         <v>28000</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="V101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W101" s="3">
         <v>17600</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y101" s="3">
         <v>45000</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA101" s="3">
         <v>31800</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-30300</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AD101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-97600</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AF101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
+        <v>453900</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
+        <v>-1719400</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
+        <v>-774900</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M102" s="3">
         <v>-12997300</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="3">
         <v>14271800</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3">
         <v>1921600</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W102" s="3">
         <v>-661100</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3">
         <v>425800</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="3">
         <v>477600</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-5270000</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="3">
         <v>5585300</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3">
         <v>672600</v>
       </c>
-      <c r="AG102" s="3" t="s">
+      <c r="AH102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="92">
   <si>
     <t>LVMUY</t>
   </si>
@@ -656,441 +656,453 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>22364000</v>
+        <v>46161400</v>
       </c>
       <c r="E8" s="3">
-        <v>47456800</v>
+        <v>22920700</v>
       </c>
       <c r="F8" s="3">
-        <v>21575100</v>
+        <v>48638000</v>
       </c>
       <c r="G8" s="3">
-        <v>45648800</v>
+        <v>22112100</v>
       </c>
       <c r="H8" s="3">
-        <v>22732500</v>
+        <v>46785000</v>
       </c>
       <c r="I8" s="3">
-        <v>45881100</v>
+        <v>23298400</v>
       </c>
       <c r="J8" s="3">
+        <v>47023200</v>
+      </c>
+      <c r="K8" s="3">
         <v>21349200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>39964800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19533300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>38539800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16704900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>30327600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14249300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>26189700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12408100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>20065100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11963900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>33373900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16312000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>29506500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14998000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>29662400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>12603400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>23881500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>12178100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>25718300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11647400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>22118900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11601900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>23959800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10726300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3">
-        <v>15079000</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3">
-        <v>13965900</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3">
-        <v>14665100</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="D9" s="3">
+        <v>14381100</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>15454300</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3">
+        <v>14313500</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="3">
+        <v>15030100</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3">
         <v>12423900</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>12191800</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>9635200</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>8845900</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>7638600</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>11295900</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>9937100</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>10048700</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="3">
         <v>7828700</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="3">
         <v>8866000</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE9" s="3">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="3">
         <v>7720400</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG9" s="3">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH9" s="3">
         <v>8359900</v>
       </c>
-      <c r="AH9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3">
-        <v>32377800</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3">
-        <v>31682900</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3">
-        <v>31216000</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="D10" s="3">
+        <v>31780400</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
+        <v>33183700</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3">
+        <v>32471500</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3">
+        <v>31993000</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" s="3">
         <v>27540900</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3">
         <v>26348000</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>20692400</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>17343800</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>12426600</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>22078100</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>19569400</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>19613700</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="3">
         <v>16052800</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="3">
         <v>16852300</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE10" s="3">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="3">
         <v>14398500</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG10" s="3">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="3">
         <v>15599900</v>
       </c>
-      <c r="AH10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1137,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1236,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,106 +1337,112 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
-        <v>224800</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
-        <v>8600</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
-        <v>188000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="D14" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>230400</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>8900</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>192700</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>117500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>94300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>32800</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>150600</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>136400</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>101600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>48200</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>62700</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="3">
         <v>80200</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
         <v>150300</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF14" s="3">
         <v>111100</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH14" s="3">
         <v>159600</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1508,8 +1530,8 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>5</v>
+      <c r="AF15" s="3">
+        <v>0</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>5</v>
@@ -1517,8 +1539,11 @@
       <c r="AH15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1575,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="3">
-        <v>35573400</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="3">
-        <v>33151600</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="3">
-        <v>34129600</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="D17" s="3">
+        <v>34394300</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3">
+        <v>36458900</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3">
+        <v>33976700</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3">
+        <v>34979100</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3">
         <v>28945600</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>28179000</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3">
         <v>22300500</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>19751500</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>18410200</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>26332100</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>23341000</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>23394200</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="3">
         <v>18854900</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="3">
         <v>20593000</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="3">
         <v>18141500</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH17" s="3">
         <v>19282200</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3">
-        <v>11883400</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="3">
-        <v>12497200</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" s="3">
-        <v>11751500</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="D18" s="3">
+        <v>11767100</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3">
+        <v>12179200</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3">
+        <v>12808300</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3">
+        <v>12044000</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3">
         <v>11019200</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>10360700</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <v>8027000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>6438200</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>1654900</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>7041800</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>6165500</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>6268200</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>5026600</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>5125300</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF18" s="3">
         <v>3977500</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH18" s="3">
         <v>4677600</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,129 +1814,133 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-901300</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="3">
-        <v>942400</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3">
-        <v>174000</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="D20" s="3">
+        <v>348900</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-923700</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3">
+        <v>965800</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
+        <v>178300</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-725800</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>181000</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>153400</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>4000</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>-268400</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>-151800</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>20000</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-332400</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>56000</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>57200</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF20" s="3">
         <v>66200</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-248800</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3">
-        <v>18738300</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3">
-        <v>16767100</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3">
-        <v>18654000</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>15704700</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3">
+        <v>19204700</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3">
+        <v>17184400</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="3">
+        <v>19118300</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1912,368 +1948,380 @@
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3">
         <v>16862100</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>12476500</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>10093400</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>8966500</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>7397900</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>6253100</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>6715100</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>5176900</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>5954700</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3">
-        <v>613800</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="3">
-        <v>437700</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="3">
-        <v>271300</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="D22" s="3">
+        <v>631300</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
+        <v>629100</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3">
+        <v>448600</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3">
+        <v>278000</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3">
         <v>142500</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3">
         <v>110600</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3">
         <v>140700</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3">
         <v>149600</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>235600</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>261500</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>261200</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="3">
         <v>100500</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB22" s="3">
         <v>80200</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="3">
         <v>102100</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF22" s="3">
         <v>87500</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH22" s="3">
         <v>63400</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="3">
-        <v>10368200</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="3">
-        <v>13001900</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="3">
-        <v>11654300</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="D23" s="3">
+        <v>11484700</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3">
+        <v>10626300</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3">
+        <v>13325500</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3">
+        <v>11944400</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="3">
         <v>10150900</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>10431200</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3">
         <v>8039700</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>6292600</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>1150900</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>6628600</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>5924400</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>5835200</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB23" s="3">
         <v>5002500</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="3">
         <v>5080400</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE23" s="3">
+      <c r="AE23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF23" s="3">
         <v>3956100</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG23" s="3">
+      <c r="AG23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH23" s="3">
         <v>4365400</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="3">
-        <v>2749300</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="3">
-        <v>3381500</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="3">
-        <v>3217200</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="D24" s="3">
+        <v>3106800</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
+        <v>2817700</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>3465700</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3">
+        <v>3297300</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="3">
         <v>2595100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3">
         <v>2710300</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3">
         <v>2128700</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>1893100</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>557500</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>1752300</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>1683400</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3">
         <v>1460900</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB24" s="3">
         <v>1387900</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD24" s="3">
         <v>1154500</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF24" s="3">
         <v>1329600</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG24" s="3">
+      <c r="AG24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH24" s="3">
         <v>1430900</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2418,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="3">
-        <v>7618900</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" s="3">
-        <v>9620400</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I26" s="3">
-        <v>8437000</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="D26" s="3">
+        <v>8377900</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3">
+        <v>7808600</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3">
+        <v>9859900</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3">
+        <v>8647000</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3">
         <v>7555800</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>7721000</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3">
         <v>5911000</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>4399500</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>593500</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>4876300</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>4240900</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>4374400</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="3">
         <v>3614600</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD26" s="3">
         <v>3925800</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF26" s="3">
         <v>2626600</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH26" s="3">
         <v>2934500</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="3">
-        <v>7233100</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="3">
-        <v>9165400</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" s="3">
-        <v>8161400</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="D27" s="3">
+        <v>8048900</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3">
+        <v>7413200</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3">
+        <v>9393600</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3">
+        <v>8364600</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3">
         <v>7107500</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>7314400</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3">
         <v>5607400</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>4169100</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>569500</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>4556400</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>3844500</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>3962700</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="3">
         <v>3298400</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD27" s="3">
         <v>3633000</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF27" s="3">
         <v>2386500</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH27" s="3">
         <v>2664500</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2721,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2822,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2923,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3024,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3">
-        <v>901300</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-942400</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-174000</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="D32" s="3">
+        <v>-348900</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
+        <v>923700</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-965800</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-178300</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>725800</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>-181000</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>-153400</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>-4000</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>268400</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>151800</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>-20000</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>332400</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-57200</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-66200</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH32" s="3">
         <v>248800</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="3">
-        <v>7233100</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="3">
-        <v>9165400</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" s="3">
-        <v>8161400</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="D33" s="3">
+        <v>8048900</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3">
+        <v>7413200</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3">
+        <v>9393600</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3">
+        <v>8364600</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3">
         <v>7107500</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>7314400</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3">
         <v>5607400</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>4169100</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>569500</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>4556400</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>3844500</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>3962700</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB33" s="3">
         <v>3298400</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD33" s="3">
         <v>3633000</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF33" s="3">
         <v>2386500</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH33" s="3">
         <v>2664500</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3327,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E35" s="3">
-        <v>7233100</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="3">
-        <v>9165400</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" s="3">
-        <v>8161400</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="D35" s="3">
+        <v>8048900</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3">
+        <v>7413200</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3">
+        <v>9393600</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3">
+        <v>8364600</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3">
         <v>7107500</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>7314400</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3">
         <v>5607400</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>4169100</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>569500</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>4556400</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>3844500</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>3962700</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="3">
         <v>3298400</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD35" s="3">
         <v>3633000</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF35" s="3">
         <v>2386500</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH35" s="3">
         <v>2664500</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3573,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,28 +3610,29 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8401400</v>
+        <v>7924900</v>
       </c>
       <c r="E41" s="3">
-        <v>6640900</v>
+        <v>8610500</v>
       </c>
       <c r="F41" s="3">
-        <v>7889100</v>
+        <v>6806200</v>
       </c>
       <c r="G41" s="3">
-        <v>8536400</v>
+        <v>8085500</v>
       </c>
       <c r="H41" s="3">
-        <v>8668300</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>5</v>
+        <v>8748900</v>
+      </c>
+      <c r="I41" s="3">
+        <v>8884100</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>5</v>
@@ -3581,70 +3667,73 @@
       <c r="T41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V41" s="3">
         <v>6622700</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W41" s="3">
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3">
         <v>4704400</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z41" s="3">
         <v>5453200</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3">
         <v>4635800</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" s="3">
         <v>4194000</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF41" s="3">
         <v>9479700</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH41" s="3">
         <v>4160000</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3771600</v>
+        <v>4349500</v>
       </c>
       <c r="E42" s="3">
-        <v>4563800</v>
+        <v>3865500</v>
       </c>
       <c r="F42" s="3">
-        <v>3838600</v>
+        <v>4677400</v>
       </c>
       <c r="G42" s="3">
-        <v>2699600</v>
+        <v>3934200</v>
       </c>
       <c r="H42" s="3">
-        <v>2749300</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>5</v>
+        <v>2766800</v>
+      </c>
+      <c r="I42" s="3">
+        <v>2817700</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>5</v>
@@ -3679,70 +3768,73 @@
       <c r="T42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U42" s="3">
+      <c r="U42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V42" s="3">
         <v>855700</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W42" s="3">
+      <c r="W42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X42" s="3">
         <v>927000</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y42" s="3">
+      <c r="Y42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z42" s="3">
         <v>787800</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB42" s="3">
         <v>799300</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC42" s="3">
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="3">
         <v>577800</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="3">
         <v>572200</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH42" s="3">
         <v>439000</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8585100</v>
+        <v>8828700</v>
       </c>
       <c r="E43" s="3">
-        <v>7662200</v>
+        <v>8798800</v>
       </c>
       <c r="F43" s="3">
-        <v>7683800</v>
+        <v>7852900</v>
       </c>
       <c r="G43" s="3">
-        <v>7174800</v>
+        <v>7875000</v>
       </c>
       <c r="H43" s="3">
-        <v>6605200</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
+        <v>7353400</v>
+      </c>
+      <c r="I43" s="3">
+        <v>6769700</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
@@ -3777,70 +3869,73 @@
       <c r="T43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V43" s="3">
         <v>6420800</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W43" s="3">
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="3">
         <v>5759700</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z43" s="3">
         <v>5939300</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3">
         <v>4967400</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
         <v>5413600</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF43" s="3">
         <v>4061600</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH43" s="3">
         <v>4816100</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>24804200</v>
+        <v>26909100</v>
       </c>
       <c r="E44" s="3">
-        <v>24464900</v>
+        <v>25421600</v>
       </c>
       <c r="F44" s="3">
-        <v>21958700</v>
+        <v>25073800</v>
       </c>
       <c r="G44" s="3">
-        <v>20446800</v>
+        <v>22505300</v>
       </c>
       <c r="H44" s="3">
-        <v>17884500</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
+        <v>20955800</v>
+      </c>
+      <c r="I44" s="3">
+        <v>18329700</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
@@ -3875,70 +3970,73 @@
       <c r="T44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U44" s="3">
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V44" s="3">
         <v>16013400</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W44" s="3">
+      <c r="W44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X44" s="3">
         <v>15953200</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="3">
         <v>14768500</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="3">
         <v>13047500</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD44" s="3">
         <v>12216200</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF44" s="3">
         <v>12190400</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH44" s="3">
         <v>12379000</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1675100</v>
+        <v>1745600</v>
       </c>
       <c r="E45" s="3">
-        <v>2059800</v>
+        <v>1716800</v>
       </c>
       <c r="F45" s="3">
-        <v>1576700</v>
+        <v>2111100</v>
       </c>
       <c r="G45" s="3">
-        <v>1442700</v>
+        <v>1616000</v>
       </c>
       <c r="H45" s="3">
-        <v>1161800</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
+        <v>1478600</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1190700</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
@@ -3973,70 +4071,73 @@
       <c r="T45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V45" s="3">
         <v>1035500</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W45" s="3">
+      <c r="W45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X45" s="3">
         <v>1014100</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z45" s="3">
         <v>909700</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB45" s="3">
         <v>888300</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD45" s="3">
         <v>1228600</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF45" s="3">
         <v>1173600</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH45" s="3">
         <v>975400</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>47237400</v>
+        <v>49757800</v>
       </c>
       <c r="E46" s="3">
-        <v>45391600</v>
+        <v>48413200</v>
       </c>
       <c r="F46" s="3">
-        <v>42947000</v>
+        <v>46521400</v>
       </c>
       <c r="G46" s="3">
-        <v>40300400</v>
+        <v>44016000</v>
       </c>
       <c r="H46" s="3">
-        <v>37069100</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>5</v>
+        <v>41303500</v>
+      </c>
+      <c r="I46" s="3">
+        <v>37991800</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>5</v>
@@ -4071,70 +4172,73 @@
       <c r="T46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V46" s="3">
         <v>30948000</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W46" s="3">
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X46" s="3">
         <v>28358300</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z46" s="3">
         <v>27858500</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB46" s="3">
         <v>24338300</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AC46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD46" s="3">
         <v>23630200</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF46" s="3">
         <v>27477500</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH46" s="3">
         <v>22769600</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3430100</v>
+        <v>3721500</v>
       </c>
       <c r="E47" s="3">
-        <v>3612800</v>
+        <v>3515500</v>
       </c>
       <c r="F47" s="3">
-        <v>3429100</v>
+        <v>3702700</v>
       </c>
       <c r="G47" s="3">
-        <v>3705700</v>
+        <v>3514400</v>
       </c>
       <c r="H47" s="3">
-        <v>3611700</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
+        <v>3798000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>3701600</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
@@ -4169,70 +4273,73 @@
       <c r="T47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>3162500</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3">
         <v>2750400</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
         <v>2862600</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3">
         <v>2390300</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
         <v>2257400</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF47" s="3">
         <v>2228300</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH47" s="3">
         <v>2461500</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>46130800</v>
+        <v>49042300</v>
       </c>
       <c r="E48" s="3">
-        <v>42500700</v>
+        <v>47279000</v>
       </c>
       <c r="F48" s="3">
-        <v>40404100</v>
+        <v>43558600</v>
       </c>
       <c r="G48" s="3">
-        <v>38273000</v>
+        <v>41409800</v>
       </c>
       <c r="H48" s="3">
-        <v>36301800</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
+        <v>39225700</v>
+      </c>
+      <c r="I48" s="3">
+        <v>37205400</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
@@ -4267,70 +4374,73 @@
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>35699400</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>32928600</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>17876000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>15549900</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>30370000</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>27241900</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" s="3">
         <v>14248900</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>53963700</v>
+        <v>52707400</v>
       </c>
       <c r="E49" s="3">
-        <v>54800100</v>
+        <v>55306900</v>
       </c>
       <c r="F49" s="3">
-        <v>54572100</v>
+        <v>56164200</v>
       </c>
       <c r="G49" s="3">
-        <v>55398800</v>
+        <v>55930500</v>
       </c>
       <c r="H49" s="3">
-        <v>54858500</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
+        <v>56777800</v>
+      </c>
+      <c r="I49" s="3">
+        <v>56224000</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
@@ -4365,50 +4475,53 @@
       <c r="T49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U49" s="3">
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V49" s="3">
         <v>39234300</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W49" s="3">
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="3">
         <v>39610600</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z49" s="3">
         <v>36647400</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3">
         <v>34095100</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD49" s="3">
         <v>68466100</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF49" s="3">
         <v>56139900</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH49" s="3">
         <v>27861600</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4618,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,28 +4719,31 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4528100</v>
+        <v>4762700</v>
       </c>
       <c r="E52" s="3">
-        <v>4317400</v>
+        <v>4640800</v>
       </c>
       <c r="F52" s="3">
-        <v>4159600</v>
+        <v>4424900</v>
       </c>
       <c r="G52" s="3">
-        <v>4227700</v>
+        <v>4263200</v>
       </c>
       <c r="H52" s="3">
-        <v>3582500</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
+        <v>4332900</v>
+      </c>
+      <c r="I52" s="3">
+        <v>3671700</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
@@ -4659,50 +4778,53 @@
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="3">
         <v>3619000</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>3315100</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>2645000</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>2396900</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>2273200</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>2462800</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3">
         <v>2643400</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,28 +4921,31 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>155290100</v>
+        <v>159991700</v>
       </c>
       <c r="E54" s="3">
-        <v>150622600</v>
+        <v>159155500</v>
       </c>
       <c r="F54" s="3">
-        <v>145511900</v>
+        <v>154371800</v>
       </c>
       <c r="G54" s="3">
-        <v>141905600</v>
+        <v>149133900</v>
       </c>
       <c r="H54" s="3">
-        <v>135423600</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>5</v>
+        <v>145437800</v>
+      </c>
+      <c r="I54" s="3">
+        <v>138794500</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>5</v>
@@ -4855,50 +4980,53 @@
       <c r="T54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V54" s="3">
         <v>112663200</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W54" s="3">
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X54" s="3">
         <v>106963000</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="3">
         <v>87889500</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="3">
         <v>78770500</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD54" s="3">
         <v>78264400</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF54" s="3">
         <v>73859500</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH54" s="3">
         <v>69984900</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5061,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,28 +5098,29 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9779300</v>
+        <v>9093400</v>
       </c>
       <c r="E57" s="3">
-        <v>8887700</v>
+        <v>10022700</v>
       </c>
       <c r="F57" s="3">
-        <v>9497200</v>
+        <v>9108900</v>
       </c>
       <c r="G57" s="3">
-        <v>8179800</v>
+        <v>9733600</v>
       </c>
       <c r="H57" s="3">
-        <v>7657800</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
+        <v>8383400</v>
+      </c>
+      <c r="I57" s="3">
+        <v>7848500</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
@@ -5025,70 +5155,73 @@
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>6787300</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>6073800</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>6285900</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>5059600</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>5092700</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3">
         <v>4320800</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="3">
         <v>4911200</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>14533300</v>
+        <v>16166500</v>
       </c>
       <c r="E58" s="3">
-        <v>17806700</v>
+        <v>14895000</v>
       </c>
       <c r="F58" s="3">
-        <v>12893800</v>
+        <v>18249900</v>
       </c>
       <c r="G58" s="3">
-        <v>14746200</v>
+        <v>13214800</v>
       </c>
       <c r="H58" s="3">
-        <v>11240400</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>5</v>
+        <v>15113200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>11520100</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>5</v>
@@ -5123,70 +5256,73 @@
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="3">
         <v>11395100</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3">
         <v>11668700</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>5924000</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>6213600</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>5487700</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="3">
         <v>5463000</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH58" s="3">
         <v>4013300</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>11507300</v>
+        <v>10764800</v>
       </c>
       <c r="E59" s="3">
-        <v>10362800</v>
+        <v>11793700</v>
       </c>
       <c r="F59" s="3">
-        <v>11697500</v>
+        <v>10620800</v>
       </c>
       <c r="G59" s="3">
-        <v>11585100</v>
+        <v>11988700</v>
       </c>
       <c r="H59" s="3">
-        <v>11349500</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
+        <v>11873500</v>
+      </c>
+      <c r="I59" s="3">
+        <v>11632000</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
@@ -5221,70 +5357,73 @@
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3">
         <v>8227900</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>7018400</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>7701900</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3">
         <v>6037900</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>6679200</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF59" s="3">
         <v>5213900</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH59" s="3">
         <v>6112000</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>35819800</v>
+        <v>36024700</v>
       </c>
       <c r="E60" s="3">
-        <v>37057200</v>
+        <v>36711400</v>
       </c>
       <c r="F60" s="3">
-        <v>34088500</v>
+        <v>37979600</v>
       </c>
       <c r="G60" s="3">
-        <v>34511100</v>
+        <v>34937000</v>
       </c>
       <c r="H60" s="3">
-        <v>30247700</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>5</v>
+        <v>35370100</v>
+      </c>
+      <c r="I60" s="3">
+        <v>31000600</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>5</v>
@@ -5319,70 +5458,73 @@
       <c r="T60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V60" s="3">
         <v>26410300</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W60" s="3">
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X60" s="3">
         <v>24760900</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z60" s="3">
         <v>19911800</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB60" s="3">
         <v>17311100</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AC60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD60" s="3">
         <v>16817500</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF60" s="3">
         <v>14997600</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH60" s="3">
         <v>15036500</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>27057500</v>
+        <v>28538400</v>
       </c>
       <c r="E61" s="3">
-        <v>23583000</v>
+        <v>27731000</v>
       </c>
       <c r="F61" s="3">
-        <v>25024700</v>
+        <v>24170000</v>
       </c>
       <c r="G61" s="3">
-        <v>24998800</v>
+        <v>25647600</v>
       </c>
       <c r="H61" s="3">
-        <v>25993000</v>
+        <v>25621000</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>26640000</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -5418,69 +5560,72 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>18064500</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>18501200</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>7103300</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>7347800</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>7905500</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>9213800</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>4615400</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>24651800</v>
+        <v>21795400</v>
       </c>
       <c r="E62" s="3">
-        <v>25735800</v>
+        <v>25265500</v>
       </c>
       <c r="F62" s="3">
-        <v>25226800</v>
+        <v>26376400</v>
       </c>
       <c r="G62" s="3">
-        <v>25428900</v>
+        <v>25854700</v>
       </c>
       <c r="H62" s="3">
-        <v>26326900</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
+        <v>26061800</v>
+      </c>
+      <c r="I62" s="3">
+        <v>26982200</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
@@ -5515,50 +5660,53 @@
       <c r="T62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="3">
         <v>23400700</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>22068100</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3">
         <v>20706700</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3">
         <v>19544400</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>19458700</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="3">
         <v>17915900</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH62" s="3">
         <v>17580200</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5803,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5904,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,28 +6005,31 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>89349000</v>
+        <v>88213700</v>
       </c>
       <c r="E66" s="3">
-        <v>88247800</v>
+        <v>91573000</v>
       </c>
       <c r="F66" s="3">
-        <v>85953500</v>
+        <v>90444400</v>
       </c>
       <c r="G66" s="3">
-        <v>87055800</v>
+        <v>88093000</v>
       </c>
       <c r="H66" s="3">
-        <v>84502100</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>5</v>
+        <v>89222700</v>
+      </c>
+      <c r="I66" s="3">
+        <v>86605500</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
@@ -5907,50 +6064,53 @@
       <c r="T66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V66" s="3">
         <v>69952400</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W66" s="3">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3">
         <v>67344200</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3">
         <v>49690100</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3">
         <v>45841500</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3">
         <v>45761500</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF66" s="3">
         <v>43746400</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH66" s="3">
         <v>39004500</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6145,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6244,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6345,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6446,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,28 +6547,31 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>64164400</v>
+        <v>68402100</v>
       </c>
       <c r="E72" s="3">
-        <v>60280400</v>
+        <v>65761500</v>
       </c>
       <c r="F72" s="3">
-        <v>55215100</v>
+        <v>61780800</v>
       </c>
       <c r="G72" s="3">
-        <v>49962900</v>
+        <v>56589500</v>
       </c>
       <c r="H72" s="3">
-        <v>46901300</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
+        <v>51206600</v>
+      </c>
+      <c r="I72" s="3">
+        <v>48068700</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
@@ -6433,50 +6606,53 @@
       <c r="T72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>38341200</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>35396700</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>34086400</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>29060800</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>28350400</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3">
         <v>25598200</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="3">
         <v>25760400</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6749,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6850,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,28 +6951,31 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>65941100</v>
+        <v>71778000</v>
       </c>
       <c r="E76" s="3">
-        <v>62374800</v>
+        <v>67582400</v>
       </c>
       <c r="F76" s="3">
-        <v>59558500</v>
+        <v>63927300</v>
       </c>
       <c r="G76" s="3">
-        <v>54849800</v>
+        <v>61040900</v>
       </c>
       <c r="H76" s="3">
-        <v>50921500</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>5</v>
+        <v>56215100</v>
+      </c>
+      <c r="I76" s="3">
+        <v>52189000</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
@@ -6825,50 +7010,53 @@
       <c r="T76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V76" s="3">
         <v>42710900</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W76" s="3">
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="3">
         <v>39618800</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z76" s="3">
         <v>38199400</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="3">
         <v>32929000</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC76" s="3">
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD76" s="3">
         <v>32502900</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF76" s="3">
         <v>30113100</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH76" s="3">
         <v>30980400</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7153,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E81" s="3">
-        <v>7233100</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G81" s="3">
-        <v>9165400</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I81" s="3">
-        <v>8161400</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="D81" s="3">
+        <v>8048900</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3">
+        <v>7413200</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3">
+        <v>9393600</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3">
+        <v>8364600</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3">
         <v>7107500</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>7314400</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3">
         <v>5607400</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>4169100</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>569500</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>4556400</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>3844500</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>3962700</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="3">
         <v>3298400</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD81" s="3">
         <v>3633000</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF81" s="3">
         <v>2386500</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH81" s="3">
         <v>2664500</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7399,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="3">
-        <v>7756200</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3">
-        <v>3327500</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I83" s="3">
-        <v>6728400</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="D83" s="3">
+        <v>3588600</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3">
+        <v>7949200</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3">
+        <v>3410300</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3">
+        <v>6895900</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>6320300</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>6034300</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>3203400</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>2781000</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1462100</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>1170500</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>1532600</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF83" s="3">
         <v>1133200</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH83" s="3">
         <v>1526000</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7599,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7700,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7801,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7902,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8003,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3">
-        <v>19884900</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3">
-        <v>7294700</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3">
-        <v>19272100</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="D89" s="3">
+        <v>8067800</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3">
+        <v>20379800</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3">
+        <v>7476300</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3">
+        <v>19751800</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
         <v>20216300</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>10868700</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>8707700</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>4927900</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>6303700</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>3470800</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>5345200</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>2542400</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH89" s="3">
         <v>5407700</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8143,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2597000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4204000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3603000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3314000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1768000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1523000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1141000</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1197000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1978800</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V91" s="3">
         <v>-2034800</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-1314000</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-1961200</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-1038700</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-1257800</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-861700</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-1928600</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8343,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8444,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-8980600</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-4425500</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-6397700</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="D94" s="3">
+        <v>-3504400</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-9204200</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-4535600</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-6557000</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>-17322800</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-2931400</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-2896300</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-3985600</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-2602400</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-1360400</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-8053600</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-1603300</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-1367500</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,31 +8584,32 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-4284200</v>
       </c>
       <c r="E96" s="3">
-        <v>-7161800</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-7340100</v>
       </c>
       <c r="G96" s="3">
-        <v>-4026700</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-4126900</v>
       </c>
       <c r="I96" s="3">
-        <v>-6865700</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-7036600</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8385,11 +8618,11 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-4510900</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -8397,11 +8630,11 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-2427700</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -8409,49 +8642,52 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-1367000</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-2837500</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1190000</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1876500</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-902100</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1465300</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-826400</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8784,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8885,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8986,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-10155300</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-4335800</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-13708700</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="D100" s="3">
+        <v>-5477100</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-10408100</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-4443700</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-14049900</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>-16430600</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>7383800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>-3917800</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>-1621100</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-3320400</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-1664600</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-2373000</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>4794300</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-3366500</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-295000</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-252900</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3">
-        <v>59400</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="D101" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-302400</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-259200</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3">
+        <v>60900</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
         <v>539900</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>-1049300</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>28000</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>17600</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>45000</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="3">
         <v>31800</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-30300</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-97600</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" s="3">
-        <v>453900</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-1719400</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-774900</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="D102" s="3">
+        <v>-893800</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3">
+        <v>465200</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-1762200</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-794100</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
         <v>-12997300</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>14271800</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>1921600</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>-661100</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>425800</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>477600</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-5270000</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>5585300</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="3">
         <v>672600</v>
       </c>
-      <c r="AH102" s="3" t="s">
+      <c r="AI102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="92">
   <si>
     <t>LVMUY</t>
   </si>
@@ -662,8 +662,7 @@
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -803,26 +802,26 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>46161400</v>
-      </c>
-      <c r="E8" s="3">
-        <v>22920700</v>
-      </c>
-      <c r="F8" s="3">
-        <v>48638000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>22112100</v>
-      </c>
-      <c r="H8" s="3">
-        <v>46785000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>23298400</v>
-      </c>
-      <c r="J8" s="3">
-        <v>47023200</v>
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K8" s="3">
         <v>21349200</v>
@@ -904,26 +903,26 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>14381100</v>
+      <c r="D9" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="3">
-        <v>15454300</v>
+      <c r="F9" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="3">
-        <v>14313500</v>
+      <c r="H9" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="3">
-        <v>15030100</v>
+      <c r="J9" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -1005,26 +1004,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>31780400</v>
+      <c r="D10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="3">
-        <v>33183700</v>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="3">
-        <v>32471500</v>
+      <c r="H10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="3">
-        <v>31993000</v>
+      <c r="J10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1345,26 +1344,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>31000</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
-        <v>230400</v>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
-        <v>8900</v>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="3">
-        <v>192700</v>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
@@ -1446,26 +1445,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1581,26 +1580,26 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>34394300</v>
+      <c r="D17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F17" s="3">
-        <v>36458900</v>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="3">
-        <v>33976700</v>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J17" s="3">
-        <v>34979100</v>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>5</v>
@@ -1682,26 +1681,26 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>11767100</v>
+      <c r="D18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="3">
-        <v>12179200</v>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="3">
-        <v>12808300</v>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J18" s="3">
-        <v>12044000</v>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>5</v>
@@ -1820,26 +1819,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>348900</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="3">
-        <v>-923700</v>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="3">
-        <v>965800</v>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J20" s="3">
-        <v>178300</v>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
@@ -1921,26 +1920,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>15704700</v>
+      <c r="D21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="3">
-        <v>19204700</v>
+      <c r="F21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H21" s="3">
-        <v>17184400</v>
+      <c r="H21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J21" s="3">
-        <v>19118300</v>
+      <c r="J21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -2022,26 +2021,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>631300</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="3">
-        <v>629100</v>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="3">
-        <v>448600</v>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J22" s="3">
-        <v>278000</v>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>5</v>
@@ -2123,26 +2122,26 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>11484700</v>
+      <c r="D23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="3">
-        <v>10626300</v>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H23" s="3">
-        <v>13325500</v>
+      <c r="H23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J23" s="3">
-        <v>11944400</v>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>5</v>
@@ -2224,26 +2223,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>3106800</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F24" s="3">
-        <v>2817700</v>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H24" s="3">
-        <v>3465700</v>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J24" s="3">
-        <v>3297300</v>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>5</v>
@@ -2426,26 +2425,26 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>8377900</v>
+      <c r="D26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F26" s="3">
-        <v>7808600</v>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H26" s="3">
-        <v>9859900</v>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J26" s="3">
-        <v>8647000</v>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>5</v>
@@ -2527,26 +2526,26 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>8048900</v>
+      <c r="D27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F27" s="3">
-        <v>7413200</v>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H27" s="3">
-        <v>9393600</v>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J27" s="3">
-        <v>8364600</v>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>5</v>
@@ -2729,26 +2728,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -3032,26 +3031,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-348900</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F32" s="3">
-        <v>923700</v>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H32" s="3">
-        <v>-965800</v>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J32" s="3">
-        <v>-178300</v>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
@@ -3133,26 +3132,26 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>8048900</v>
+      <c r="D33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F33" s="3">
-        <v>7413200</v>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H33" s="3">
-        <v>9393600</v>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J33" s="3">
-        <v>8364600</v>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>5</v>
@@ -3335,26 +3334,26 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>8048900</v>
+      <c r="D35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="3">
-        <v>7413200</v>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H35" s="3">
-        <v>9393600</v>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J35" s="3">
-        <v>8364600</v>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>5</v>
@@ -3617,25 +3616,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7924900</v>
+        <v>7666300</v>
       </c>
       <c r="E41" s="3">
-        <v>8610500</v>
+        <v>7719300</v>
       </c>
       <c r="F41" s="3">
-        <v>6806200</v>
+        <v>8592900</v>
       </c>
       <c r="G41" s="3">
-        <v>8085500</v>
+        <v>8228200</v>
       </c>
       <c r="H41" s="3">
-        <v>8748900</v>
+        <v>6708500</v>
       </c>
       <c r="I41" s="3">
-        <v>8884100</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>5</v>
+        <v>6676400</v>
+      </c>
+      <c r="J41" s="3">
+        <v>7801600</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>5</v>
@@ -3718,25 +3717,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4349500</v>
+        <v>4223700</v>
       </c>
       <c r="E42" s="3">
-        <v>3865500</v>
+        <v>4252900</v>
       </c>
       <c r="F42" s="3">
-        <v>4677400</v>
+        <v>3883100</v>
       </c>
       <c r="G42" s="3">
-        <v>3934200</v>
+        <v>3718200</v>
       </c>
       <c r="H42" s="3">
-        <v>2766800</v>
+        <v>4625500</v>
       </c>
       <c r="I42" s="3">
-        <v>2817700</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>5</v>
+        <v>4603400</v>
+      </c>
+      <c r="J42" s="3">
+        <v>3830300</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>5</v>
@@ -3819,25 +3818,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8828700</v>
+        <v>8540700</v>
       </c>
       <c r="E43" s="3">
-        <v>8798800</v>
+        <v>8599600</v>
       </c>
       <c r="F43" s="3">
-        <v>7852900</v>
+        <v>8780800</v>
       </c>
       <c r="G43" s="3">
-        <v>7875000</v>
+        <v>8408100</v>
       </c>
       <c r="H43" s="3">
-        <v>7353400</v>
+        <v>7742400</v>
       </c>
       <c r="I43" s="3">
-        <v>6769700</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
+        <v>7705300</v>
+      </c>
+      <c r="J43" s="3">
+        <v>7598600</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
@@ -3920,25 +3919,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>26909100</v>
+        <v>26031300</v>
       </c>
       <c r="E44" s="3">
-        <v>25421600</v>
+        <v>26211000</v>
       </c>
       <c r="F44" s="3">
-        <v>25073800</v>
+        <v>25369700</v>
       </c>
       <c r="G44" s="3">
-        <v>22505300</v>
+        <v>24293000</v>
       </c>
       <c r="H44" s="3">
-        <v>20955800</v>
+        <v>24714000</v>
       </c>
       <c r="I44" s="3">
-        <v>18329700</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
+        <v>24595800</v>
+      </c>
+      <c r="J44" s="3">
+        <v>21715300</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>5</v>
@@ -4021,25 +4020,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1745600</v>
+        <v>807900</v>
       </c>
       <c r="E45" s="3">
-        <v>1716800</v>
+        <v>813500</v>
       </c>
       <c r="F45" s="3">
-        <v>2111100</v>
+        <v>935100</v>
       </c>
       <c r="G45" s="3">
-        <v>1616000</v>
+        <v>895400</v>
       </c>
       <c r="H45" s="3">
-        <v>1478600</v>
+        <v>1288200</v>
       </c>
       <c r="I45" s="3">
-        <v>1190700</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
+        <v>1282100</v>
+      </c>
+      <c r="J45" s="3">
+        <v>869900</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
@@ -4122,25 +4121,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>49757800</v>
+        <v>48134600</v>
       </c>
       <c r="E46" s="3">
-        <v>48413200</v>
+        <v>48466900</v>
       </c>
       <c r="F46" s="3">
-        <v>46521400</v>
+        <v>48314400</v>
       </c>
       <c r="G46" s="3">
-        <v>44016000</v>
+        <v>46263800</v>
       </c>
       <c r="H46" s="3">
-        <v>41303500</v>
+        <v>45853700</v>
       </c>
       <c r="I46" s="3">
-        <v>37991800</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>5</v>
+        <v>45634500</v>
+      </c>
+      <c r="J46" s="3">
+        <v>42470900</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>5</v>
@@ -4223,25 +4222,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3721500</v>
+        <v>2715100</v>
       </c>
       <c r="E47" s="3">
-        <v>3515500</v>
+        <v>2733800</v>
       </c>
       <c r="F47" s="3">
-        <v>3702700</v>
+        <v>2604200</v>
       </c>
       <c r="G47" s="3">
-        <v>3514400</v>
+        <v>2493600</v>
       </c>
       <c r="H47" s="3">
-        <v>3798000</v>
+        <v>2699800</v>
       </c>
       <c r="I47" s="3">
-        <v>3701600</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
+        <v>2686900</v>
+      </c>
+      <c r="J47" s="3">
+        <v>2324500</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>5</v>
@@ -4324,25 +4323,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>49042300</v>
+        <v>47777800</v>
       </c>
       <c r="E48" s="3">
-        <v>47279000</v>
+        <v>48107700</v>
       </c>
       <c r="F48" s="3">
-        <v>43558600</v>
+        <v>47540600</v>
       </c>
       <c r="G48" s="3">
-        <v>41409800</v>
+        <v>45522900</v>
       </c>
       <c r="H48" s="3">
-        <v>39225700</v>
+        <v>43245600</v>
       </c>
       <c r="I48" s="3">
-        <v>37205400</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
+        <v>43038900</v>
+      </c>
+      <c r="J48" s="3">
+        <v>40258600</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
@@ -4425,25 +4424,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>52707400</v>
+        <v>50652500</v>
       </c>
       <c r="E49" s="3">
-        <v>55306900</v>
+        <v>51002300</v>
       </c>
       <c r="F49" s="3">
-        <v>56164200</v>
+        <v>54837000</v>
       </c>
       <c r="G49" s="3">
-        <v>55930500</v>
+        <v>52509500</v>
       </c>
       <c r="H49" s="3">
-        <v>56777800</v>
+        <v>55044800</v>
       </c>
       <c r="I49" s="3">
-        <v>56224000</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
+        <v>54781600</v>
+      </c>
+      <c r="J49" s="3">
+        <v>53664600</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>5</v>
@@ -4728,25 +4727,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4762700</v>
+        <v>851800</v>
       </c>
       <c r="E52" s="3">
-        <v>4640800</v>
+        <v>857700</v>
       </c>
       <c r="F52" s="3">
-        <v>4424900</v>
+        <v>853300</v>
       </c>
       <c r="G52" s="3">
-        <v>4263200</v>
+        <v>817100</v>
       </c>
       <c r="H52" s="3">
-        <v>4332900</v>
+        <v>845000</v>
       </c>
       <c r="I52" s="3">
-        <v>3671700</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
+        <v>840900</v>
+      </c>
+      <c r="J52" s="3">
+        <v>793000</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
@@ -4930,25 +4929,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>159991700</v>
+        <v>154772300</v>
       </c>
       <c r="E54" s="3">
-        <v>159155500</v>
+        <v>155841000</v>
       </c>
       <c r="F54" s="3">
-        <v>154371800</v>
+        <v>158830600</v>
       </c>
       <c r="G54" s="3">
-        <v>149133900</v>
+        <v>152089300</v>
       </c>
       <c r="H54" s="3">
-        <v>145437800</v>
+        <v>152156100</v>
       </c>
       <c r="I54" s="3">
-        <v>138794500</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>5</v>
+        <v>151428700</v>
+      </c>
+      <c r="J54" s="3">
+        <v>143898700</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>5</v>
@@ -5105,25 +5104,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9093400</v>
+        <v>8796700</v>
       </c>
       <c r="E57" s="3">
-        <v>10022700</v>
+        <v>8857500</v>
       </c>
       <c r="F57" s="3">
-        <v>9108900</v>
+        <v>10002200</v>
       </c>
       <c r="G57" s="3">
-        <v>9733600</v>
+        <v>9577700</v>
       </c>
       <c r="H57" s="3">
-        <v>8383400</v>
+        <v>8978200</v>
       </c>
       <c r="I57" s="3">
-        <v>7848500</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
+        <v>8935200</v>
+      </c>
+      <c r="J57" s="3">
+        <v>9391900</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>5</v>
@@ -5206,25 +5205,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>16166500</v>
+        <v>16050600</v>
       </c>
       <c r="E58" s="3">
-        <v>14895000</v>
+        <v>16161400</v>
       </c>
       <c r="F58" s="3">
-        <v>18249900</v>
+        <v>15320000</v>
       </c>
       <c r="G58" s="3">
-        <v>13214800</v>
+        <v>14669800</v>
       </c>
       <c r="H58" s="3">
-        <v>15113200</v>
+        <v>17861400</v>
       </c>
       <c r="I58" s="3">
-        <v>11520100</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>5</v>
+        <v>17776000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>13178400</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>5</v>
@@ -5307,25 +5306,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10764800</v>
+        <v>6018400</v>
       </c>
       <c r="E59" s="3">
-        <v>11793700</v>
+        <v>6060000</v>
       </c>
       <c r="F59" s="3">
-        <v>10620800</v>
+        <v>6453000</v>
       </c>
       <c r="G59" s="3">
-        <v>11988700</v>
+        <v>6179100</v>
       </c>
       <c r="H59" s="3">
-        <v>11873500</v>
+        <v>6852600</v>
       </c>
       <c r="I59" s="3">
-        <v>11632000</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>5</v>
+        <v>6819900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>6874000</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>5</v>
@@ -5408,25 +5407,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>36024700</v>
+        <v>34849500</v>
       </c>
       <c r="E60" s="3">
-        <v>36711400</v>
+        <v>35090100</v>
       </c>
       <c r="F60" s="3">
-        <v>37979600</v>
+        <v>36636500</v>
       </c>
       <c r="G60" s="3">
-        <v>34937000</v>
+        <v>35081500</v>
       </c>
       <c r="H60" s="3">
-        <v>35370100</v>
+        <v>37434500</v>
       </c>
       <c r="I60" s="3">
-        <v>31000600</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>5</v>
+        <v>37255500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>33710600</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>5</v>
@@ -5509,25 +5508,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>28538400</v>
+        <v>27719900</v>
       </c>
       <c r="E61" s="3">
-        <v>27731000</v>
+        <v>27911300</v>
       </c>
       <c r="F61" s="3">
-        <v>24170000</v>
+        <v>27783800</v>
       </c>
       <c r="G61" s="3">
-        <v>25647600</v>
+        <v>26604600</v>
       </c>
       <c r="H61" s="3">
-        <v>25621000</v>
+        <v>24015300</v>
       </c>
       <c r="I61" s="3">
-        <v>26640000</v>
+        <v>23900500</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>24917200</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5610,25 +5609,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>21795400</v>
+        <v>12634700</v>
       </c>
       <c r="E62" s="3">
-        <v>25265500</v>
+        <v>12722000</v>
       </c>
       <c r="F62" s="3">
-        <v>26376400</v>
+        <v>16680700</v>
       </c>
       <c r="G62" s="3">
-        <v>25854700</v>
+        <v>15972700</v>
       </c>
       <c r="H62" s="3">
-        <v>26061800</v>
+        <v>17234700</v>
       </c>
       <c r="I62" s="3">
-        <v>26982200</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
+        <v>17152300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>16682700</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>5</v>
@@ -6014,25 +6013,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>88213700</v>
+        <v>83541200</v>
       </c>
       <c r="E66" s="3">
-        <v>91573000</v>
+        <v>84118000</v>
       </c>
       <c r="F66" s="3">
-        <v>90444400</v>
+        <v>89524700</v>
       </c>
       <c r="G66" s="3">
-        <v>88093000</v>
+        <v>85725000</v>
       </c>
       <c r="H66" s="3">
-        <v>89222700</v>
+        <v>87255500</v>
       </c>
       <c r="I66" s="3">
-        <v>86605500</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>5</v>
+        <v>86838300</v>
+      </c>
+      <c r="J66" s="3">
+        <v>83404900</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>5</v>
@@ -6556,25 +6555,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>68402100</v>
+        <v>7786300</v>
       </c>
       <c r="E72" s="3">
-        <v>65761500</v>
+        <v>7840100</v>
       </c>
       <c r="F72" s="3">
-        <v>61780800</v>
+        <v>16771300</v>
       </c>
       <c r="G72" s="3">
-        <v>56589500</v>
+        <v>16059500</v>
       </c>
       <c r="H72" s="3">
-        <v>51206600</v>
+        <v>9257600</v>
       </c>
       <c r="I72" s="3">
-        <v>48068700</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
+        <v>9213400</v>
+      </c>
+      <c r="J72" s="3">
+        <v>15052900</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>5</v>
@@ -6960,25 +6959,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>71778000</v>
+        <v>69436400</v>
       </c>
       <c r="E76" s="3">
-        <v>67582400</v>
+        <v>69915800</v>
       </c>
       <c r="F76" s="3">
-        <v>63927300</v>
+        <v>67444500</v>
       </c>
       <c r="G76" s="3">
-        <v>61040900</v>
+        <v>64581900</v>
       </c>
       <c r="H76" s="3">
-        <v>56215100</v>
+        <v>63009800</v>
       </c>
       <c r="I76" s="3">
-        <v>52189000</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>5</v>
+        <v>62708600</v>
+      </c>
+      <c r="J76" s="3">
+        <v>58898200</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>5</v>
@@ -7267,26 +7266,26 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>8048900</v>
+      <c r="D81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F81" s="3">
-        <v>7413200</v>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H81" s="3">
-        <v>9393600</v>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J81" s="3">
-        <v>8364600</v>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>5</v>
@@ -7406,25 +7405,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3588600</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
+        <v>1566600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1559100</v>
       </c>
       <c r="F83" s="3">
-        <v>7949200</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
+        <v>1225800</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1124700</v>
       </c>
       <c r="H83" s="3">
-        <v>3410300</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
+        <v>1447300</v>
+      </c>
+      <c r="I83" s="3">
+        <v>1538000</v>
       </c>
       <c r="J83" s="3">
-        <v>6895900</v>
+        <v>780200</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -8012,25 +8011,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>8067800</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
+        <v>3902300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>3929200</v>
       </c>
       <c r="F89" s="3">
-        <v>20379800</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
+        <v>6438600</v>
+      </c>
+      <c r="G89" s="3">
+        <v>6165300</v>
       </c>
       <c r="H89" s="3">
-        <v>7476300</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
+        <v>3684500</v>
+      </c>
+      <c r="I89" s="3">
+        <v>3666900</v>
       </c>
       <c r="J89" s="3">
-        <v>19751800</v>
+        <v>5646600</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>5</v>
@@ -8150,25 +8149,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2597000</v>
+        <v>-1461500</v>
       </c>
       <c r="E91" s="3">
-        <v>-4204000</v>
+        <v>-1471600</v>
       </c>
       <c r="F91" s="3">
-        <v>-3603000</v>
+        <v>-1792300</v>
       </c>
       <c r="G91" s="3">
-        <v>-3314000</v>
+        <v>-1716200</v>
       </c>
       <c r="H91" s="3">
-        <v>-1768000</v>
+        <v>-1945400</v>
       </c>
       <c r="I91" s="3">
-        <v>-1523000</v>
+        <v>-1936100</v>
       </c>
       <c r="J91" s="3">
-        <v>-1141000</v>
+        <v>-1343900</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8453,25 +8452,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3504400</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
+        <v>-1695100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1706800</v>
       </c>
       <c r="F94" s="3">
-        <v>-9204200</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
+        <v>-2329500</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-2230600</v>
       </c>
       <c r="H94" s="3">
-        <v>-4535600</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
+        <v>-2235300</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-2224600</v>
       </c>
       <c r="J94" s="3">
-        <v>-6557000</v>
+        <v>-2071200</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>5</v>
@@ -8591,25 +8590,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-4284200</v>
+        <v>2007400</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>2021300</v>
       </c>
       <c r="F96" s="3">
-        <v>-7340100</v>
+        <v>1518700</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>1454300</v>
       </c>
       <c r="H96" s="3">
-        <v>-4126900</v>
+        <v>1912100</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>1903000</v>
       </c>
       <c r="J96" s="3">
-        <v>-7036600</v>
+        <v>1338600</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8995,25 +8994,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-5477100</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
+        <v>-2649200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-2667500</v>
       </c>
       <c r="F100" s="3">
-        <v>-10408100</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
+        <v>-2976100</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-2849800</v>
       </c>
       <c r="H100" s="3">
-        <v>-4443700</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
+        <v>-2190000</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-2179500</v>
       </c>
       <c r="J100" s="3">
-        <v>-14049900</v>
+        <v>-3660900</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>5</v>
@@ -9096,25 +9095,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>19900</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
+        <v>-127700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-127100</v>
       </c>
       <c r="F101" s="3">
-        <v>-302400</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
+        <v>-127700</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-117200</v>
       </c>
       <c r="H101" s="3">
-        <v>-259200</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
+        <v>153700</v>
+      </c>
+      <c r="I101" s="3">
+        <v>163300</v>
       </c>
       <c r="J101" s="3">
-        <v>60900</v>
+        <v>212100</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>5</v>
@@ -9197,25 +9196,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-893800</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>5</v>
+        <v>-432300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-435300</v>
       </c>
       <c r="F102" s="3">
-        <v>465200</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
+        <v>1111400</v>
+      </c>
+      <c r="G102" s="3">
+        <v>1064200</v>
       </c>
       <c r="H102" s="3">
-        <v>-1762200</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
+        <v>-868400</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-864300</v>
       </c>
       <c r="J102" s="3">
-        <v>-794100</v>
+        <v>-213200</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>5</v>

--- a/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="92">
   <si>
     <t>LVMUY</t>
   </si>
@@ -656,149 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -823,83 +829,89 @@
       <c r="J8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="3">
         <v>21349200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>39964800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>19533300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>38539800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>16704900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>30327600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>14249300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>26189700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>12408100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>20065100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>11963900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>33373900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>16312000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>29506500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>14998000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>29662400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>12603400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>23881500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>12178100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>25718300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>11647400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>22118900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>11601900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>23959800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>10726300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -927,80 +939,86 @@
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>12423900</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>12191800</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>9635200</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>8845900</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>7638600</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>11295900</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>9937100</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="3">
         <v>10048700</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="3">
         <v>7828700</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="3">
         <v>8866000</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH9" s="3">
         <v>7720400</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>8359900</v>
       </c>
-      <c r="AI9" s="3" t="s">
+      <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1028,80 +1046,86 @@
       <c r="K10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3">
         <v>27540900</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>26348000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>20692400</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>17343800</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>12426600</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>22078100</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>19569400</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="3">
         <v>19613700</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="3">
         <v>16052800</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="3">
         <v>16852300</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="3">
         <v>14398500</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>15599900</v>
       </c>
-      <c r="AI10" s="3" t="s">
+      <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1137,8 +1161,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1238,8 +1264,14 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1339,8 +1371,14 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1368,80 +1406,86 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>117500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>94300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>32800</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>150600</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>136400</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>101600</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>48200</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="3">
         <v>62700</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
         <v>80200</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF14" s="3">
         <v>150300</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH14" s="3">
         <v>111100</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>159600</v>
       </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,11 +1510,11 @@
       <c r="J15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1532,17 +1576,23 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH15" s="3" t="s">
-        <v>5</v>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1575,8 +1625,10 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1604,80 +1656,86 @@
       <c r="K17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>28945600</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3">
         <v>28179000</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>22300500</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>19751500</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>18410200</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>26332100</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>23341000</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="3">
         <v>23394200</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="3">
         <v>18854900</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="3">
         <v>20593000</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH17" s="3">
         <v>18141500</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>19282200</v>
       </c>
-      <c r="AI17" s="3" t="s">
+      <c r="AK17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1705,80 +1763,86 @@
       <c r="K18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>11019200</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <v>10360700</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>8027000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>6438200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>1654900</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>7041800</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>6165500</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>6268200</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>5026600</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF18" s="3">
         <v>5125300</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH18" s="3">
         <v>3977500</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>4677600</v>
       </c>
-      <c r="AI18" s="3" t="s">
+      <c r="AK18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1814,8 +1878,10 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1843,80 +1909,86 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-725800</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>181000</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>153400</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>4000</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>-268400</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>-151800</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>20000</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-332400</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>56000</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF20" s="3">
         <v>57200</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH20" s="3">
         <v>66200</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-248800</v>
       </c>
-      <c r="AI20" s="3" t="s">
+      <c r="AK20" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1950,74 +2022,80 @@
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>16862100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>12476500</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>10093400</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>8966500</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>7397900</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>6253100</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>6715100</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>5176900</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>5954700</v>
       </c>
-      <c r="AI21" s="3" t="s">
+      <c r="AK21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2045,80 +2123,86 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3">
         <v>142500</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3">
         <v>110600</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3">
         <v>140700</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>149600</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>235600</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>261500</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="3">
         <v>261200</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB22" s="3">
         <v>100500</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="3">
         <v>80200</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF22" s="3">
         <v>102100</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH22" s="3">
         <v>87500</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>63400</v>
       </c>
-      <c r="AI22" s="3" t="s">
+      <c r="AK22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2146,80 +2230,86 @@
       <c r="K23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>10150900</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3">
         <v>10431200</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>8039700</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>6292600</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>1150900</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>6628600</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>5924400</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB23" s="3">
         <v>5835200</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="3">
         <v>5002500</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF23" s="3">
         <v>5080400</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH23" s="3">
         <v>3956100</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>4365400</v>
       </c>
-      <c r="AI23" s="3" t="s">
+      <c r="AK23" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2247,80 +2337,86 @@
       <c r="K24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3">
         <v>2595100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3">
         <v>2710300</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>2128700</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>1893100</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>557500</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>1752300</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3">
         <v>1683400</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB24" s="3">
         <v>1460900</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD24" s="3">
         <v>1387900</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF24" s="3">
         <v>1154500</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH24" s="3">
         <v>1329600</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>1430900</v>
       </c>
-      <c r="AI24" s="3" t="s">
+      <c r="AK24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2420,8 +2516,14 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2449,80 +2551,86 @@
       <c r="K26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>7555800</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3">
         <v>7721000</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>5911000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>4399500</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>593500</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>4876300</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>4240900</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="3">
         <v>4374400</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD26" s="3">
         <v>3614600</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF26" s="3">
         <v>3925800</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH26" s="3">
         <v>2626600</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>2934500</v>
       </c>
-      <c r="AI26" s="3" t="s">
+      <c r="AK26" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2550,80 +2658,86 @@
       <c r="K27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>7107500</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3">
         <v>7314400</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>5607400</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>4169100</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>569500</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>4556400</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>3844500</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="3">
         <v>3962700</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD27" s="3">
         <v>3298400</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF27" s="3">
         <v>3633000</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH27" s="3">
         <v>2386500</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>2664500</v>
       </c>
-      <c r="AI27" s="3" t="s">
+      <c r="AK27" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2723,8 +2837,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2749,11 +2869,11 @@
       <c r="J29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2824,8 +2944,14 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2925,8 +3051,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3026,8 +3158,14 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3055,80 +3193,86 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>725800</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>-181000</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>-153400</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>-4000</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>268400</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>151800</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>332400</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-57200</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-66200</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>248800</v>
       </c>
-      <c r="AI32" s="3" t="s">
+      <c r="AK32" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3156,80 +3300,86 @@
       <c r="K33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>7107500</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3">
         <v>7314400</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>5607400</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>4169100</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>569500</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>4556400</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>3844500</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB33" s="3">
         <v>3962700</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD33" s="3">
         <v>3298400</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF33" s="3">
         <v>3633000</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH33" s="3">
         <v>2386500</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>2664500</v>
       </c>
-      <c r="AI33" s="3" t="s">
+      <c r="AK33" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3329,8 +3479,14 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3358,186 +3514,198 @@
       <c r="K35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>7107500</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3">
         <v>7314400</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>5607400</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>4169100</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>569500</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>4556400</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>3844500</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="3">
         <v>3962700</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD35" s="3">
         <v>3298400</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF35" s="3">
         <v>3633000</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH35" s="3">
         <v>2386500</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>2664500</v>
       </c>
-      <c r="AI35" s="3" t="s">
+      <c r="AK35" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3573,8 +3741,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3610,38 +3780,40 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9971000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10741700</v>
+      </c>
+      <c r="F41" s="3">
         <v>7666300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>7719300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>8592900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8228200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6708500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>6676400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7801600</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>5</v>
       </c>
@@ -3669,80 +3841,86 @@
       <c r="U41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V41" s="3">
+      <c r="V41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3">
         <v>6622700</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z41" s="3">
         <v>4704400</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3">
         <v>5453200</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" s="3">
         <v>4635800</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF41" s="3">
         <v>4194000</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH41" s="3">
         <v>9479700</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>4160000</v>
       </c>
-      <c r="AI41" s="3" t="s">
+      <c r="AK41" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4118400</v>
+      </c>
+      <c r="E42" s="3">
+        <v>4436800</v>
+      </c>
+      <c r="F42" s="3">
         <v>4223700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>4252900</v>
       </c>
-      <c r="F42" s="3">
-        <v>3883100</v>
-      </c>
-      <c r="G42" s="3">
-        <v>3718200</v>
-      </c>
       <c r="H42" s="3">
+        <v>3884200</v>
+      </c>
+      <c r="I42" s="3">
+        <v>3719300</v>
+      </c>
+      <c r="J42" s="3">
         <v>4625500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>4603400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>3830300</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>5</v>
       </c>
@@ -3770,80 +3948,86 @@
       <c r="U42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V42" s="3">
+      <c r="V42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X42" s="3">
         <v>855700</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z42" s="3">
         <v>927000</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB42" s="3">
         <v>787800</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="3">
         <v>799300</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="3">
         <v>577800</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH42" s="3">
         <v>572200</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>439000</v>
       </c>
-      <c r="AI42" s="3" t="s">
+      <c r="AK42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9085800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>9788100</v>
+      </c>
+      <c r="F43" s="3">
         <v>8540700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>8599600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>8780800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>8408100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>7742400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>7705300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>7598600</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3871,80 +4055,86 @@
       <c r="U43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V43" s="3">
+      <c r="V43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="3">
         <v>6420800</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z43" s="3">
         <v>5759700</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3">
         <v>5939300</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
         <v>4967400</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF43" s="3">
         <v>5413600</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH43" s="3">
         <v>4061600</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>4816100</v>
       </c>
-      <c r="AI43" s="3" t="s">
+      <c r="AK43" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>24504600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>26398600</v>
+      </c>
+      <c r="F44" s="3">
         <v>26031300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>26211000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>25369700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>24293000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>24714000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>24595800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>21715300</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3972,80 +4162,86 @@
       <c r="U44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V44" s="3">
+      <c r="V44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X44" s="3">
         <v>16013400</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="3">
         <v>15953200</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="3">
         <v>14768500</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD44" s="3">
         <v>13047500</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF44" s="3">
         <v>12216200</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH44" s="3">
         <v>12190400</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>12379000</v>
       </c>
-      <c r="AI44" s="3" t="s">
+      <c r="AK44" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>598400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>644700</v>
+      </c>
+      <c r="F45" s="3">
         <v>807900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>813500</v>
       </c>
-      <c r="F45" s="3">
-        <v>935100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>895400</v>
-      </c>
       <c r="H45" s="3">
+        <v>934000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>894400</v>
+      </c>
+      <c r="J45" s="3">
         <v>1288200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1282100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>869900</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>5</v>
       </c>
@@ -4073,80 +4269,86 @@
       <c r="U45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X45" s="3">
         <v>1035500</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z45" s="3">
         <v>1014100</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB45" s="3">
         <v>909700</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD45" s="3">
         <v>888300</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF45" s="3">
         <v>1228600</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH45" s="3">
         <v>1173600</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>975400</v>
       </c>
-      <c r="AI45" s="3" t="s">
+      <c r="AK45" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>49146900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>52945600</v>
+      </c>
+      <c r="F46" s="3">
         <v>48134600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>48466900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>48314400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>46263800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>45853700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>45634500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>42470900</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>5</v>
       </c>
@@ -4174,80 +4376,86 @@
       <c r="U46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V46" s="3">
+      <c r="V46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X46" s="3">
         <v>30948000</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z46" s="3">
         <v>28358300</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB46" s="3">
         <v>27858500</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD46" s="3">
         <v>24338300</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF46" s="3">
         <v>23630200</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH46" s="3">
         <v>27477500</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>22769600</v>
       </c>
-      <c r="AI46" s="3" t="s">
+      <c r="AK46" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3084200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3322600</v>
+      </c>
+      <c r="F47" s="3">
         <v>2715100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>2733800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>2604200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>2493600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2699800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2686900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2324500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4275,80 +4483,86 @@
       <c r="U47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3">
         <v>3162500</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
         <v>2750400</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3">
         <v>2862600</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
         <v>2390300</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF47" s="3">
         <v>2257400</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH47" s="3">
         <v>2228300</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>2461500</v>
       </c>
-      <c r="AI47" s="3" t="s">
+      <c r="AK47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>48147800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>51869300</v>
+      </c>
+      <c r="F48" s="3">
         <v>47777800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>48107700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>47540600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>45522900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>43245600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>43038900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>40258600</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4376,80 +4590,86 @@
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V48" s="3">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>35699400</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>32928600</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>17876000</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>15549900</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>30370000</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" s="3">
         <v>27241900</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>14248900</v>
       </c>
-      <c r="AI48" s="3" t="s">
+      <c r="AK48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>48231700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>51959600</v>
+      </c>
+      <c r="F49" s="3">
         <v>50652500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>51002300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>54837000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>52509500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>55044800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>54781600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>53664600</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4477,50 +4697,56 @@
       <c r="U49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V49" s="3">
+      <c r="V49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="3">
         <v>39234300</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z49" s="3">
         <v>39610600</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3">
         <v>36647400</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD49" s="3">
         <v>34095100</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF49" s="3">
         <v>68466100</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH49" s="3">
         <v>56139900</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>27861600</v>
       </c>
-      <c r="AI49" s="3" t="s">
+      <c r="AK49" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4620,8 +4846,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4721,38 +4953,44 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>860300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>926800</v>
+      </c>
+      <c r="F52" s="3">
         <v>851800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>857700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>853300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>817100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>845000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>840900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>793000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4780,50 +5018,56 @@
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>3619000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>3315100</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>2645000</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>2396900</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>2273200</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3">
         <v>2462800</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>2643400</v>
       </c>
-      <c r="AI52" s="3" t="s">
+      <c r="AK52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4923,38 +5167,44 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>154457000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>166395300</v>
+      </c>
+      <c r="F54" s="3">
         <v>154772300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>155841000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>158830600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>152089300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>152156100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>151428700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>143898700</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>5</v>
       </c>
@@ -4982,50 +5232,56 @@
       <c r="U54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X54" s="3">
         <v>112663200</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="3">
         <v>106963000</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="3">
         <v>87889500</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD54" s="3">
         <v>78770500</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF54" s="3">
         <v>78264400</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH54" s="3">
         <v>73859500</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>69984900</v>
       </c>
-      <c r="AI54" s="3" t="s">
+      <c r="AK54" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5061,8 +5317,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5098,38 +5356,40 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8934700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>9625300</v>
+      </c>
+      <c r="F57" s="3">
         <v>8796700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>8857500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>10002200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>9577700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>8978200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>8935200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>9391900</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5157,80 +5417,86 @@
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>6787300</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>6073800</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>6285900</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>5059600</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3">
         <v>5092700</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="3">
         <v>4320800</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>4911200</v>
       </c>
-      <c r="AI57" s="3" t="s">
+      <c r="AK57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14770700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>15912300</v>
+      </c>
+      <c r="F58" s="3">
         <v>16050600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>16161400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>15320000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>14669800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>17861400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>17776000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>13178400</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>5</v>
       </c>
@@ -5258,80 +5524,86 @@
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3">
         <v>11395100</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>11668700</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>5924000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>6213600</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="3">
         <v>5487700</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH58" s="3">
         <v>5463000</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>4013300</v>
       </c>
-      <c r="AI58" s="3" t="s">
+      <c r="AK58" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6308100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6795700</v>
+      </c>
+      <c r="F59" s="3">
         <v>6018400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>6060000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>6453000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>6179100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>6852600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>6819900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>6874000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5359,80 +5631,86 @@
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>8227900</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>7018400</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3">
         <v>7701900</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>6037900</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF59" s="3">
         <v>6679200</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH59" s="3">
         <v>5213900</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>6112000</v>
       </c>
-      <c r="AI59" s="3" t="s">
+      <c r="AK59" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34885600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>37582000</v>
+      </c>
+      <c r="F60" s="3">
         <v>34849500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>35090100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>36636500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>35081500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>37434500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>37255500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>33710600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>5</v>
       </c>
@@ -5460,80 +5738,86 @@
       <c r="U60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V60" s="3">
+      <c r="V60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X60" s="3">
         <v>26410300</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z60" s="3">
         <v>24760900</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB60" s="3">
         <v>19911800</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD60" s="3">
         <v>17311100</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF60" s="3">
         <v>16817500</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH60" s="3">
         <v>14997600</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>15036500</v>
       </c>
-      <c r="AI60" s="3" t="s">
+      <c r="AK60" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>27991500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>30155000</v>
+      </c>
+      <c r="F61" s="3">
         <v>27719900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>27911300</v>
       </c>
-      <c r="F61" s="3">
-        <v>27783800</v>
-      </c>
-      <c r="G61" s="3">
-        <v>26604600</v>
-      </c>
       <c r="H61" s="3">
+        <v>27784900</v>
+      </c>
+      <c r="I61" s="3">
+        <v>26605600</v>
+      </c>
+      <c r="J61" s="3">
         <v>24015300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>23900500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>24917200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5562,79 +5846,85 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>18064500</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>18501200</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>7103300</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>7347800</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>7905500</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>9213800</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>4615400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11570600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>12464900</v>
+      </c>
+      <c r="F62" s="3">
         <v>12634700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>12722000</v>
       </c>
-      <c r="F62" s="3">
-        <v>16680700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>15972700</v>
-      </c>
       <c r="H62" s="3">
+        <v>16679600</v>
+      </c>
+      <c r="I62" s="3">
+        <v>15971600</v>
+      </c>
+      <c r="J62" s="3">
         <v>17234700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>17152300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>16682700</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>5</v>
       </c>
@@ -5662,50 +5952,56 @@
       <c r="U62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V62" s="3">
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>23400700</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3">
         <v>22068100</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3">
         <v>20706700</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>19544400</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="3">
         <v>19458700</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH62" s="3">
         <v>17915900</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>17580200</v>
       </c>
-      <c r="AI62" s="3" t="s">
+      <c r="AK62" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5805,8 +6101,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5906,8 +6208,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6007,38 +6315,44 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>82723900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>89117800</v>
+      </c>
+      <c r="F66" s="3">
         <v>83541200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>84118000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>89524700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>85725000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>87255500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>86838300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>83404900</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>5</v>
       </c>
@@ -6066,50 +6380,56 @@
       <c r="U66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3">
         <v>69952400</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3">
         <v>67344200</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3">
         <v>49690100</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3">
         <v>45841500</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF66" s="3">
         <v>45761500</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH66" s="3">
         <v>43746400</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>39004500</v>
       </c>
-      <c r="AI66" s="3" t="s">
+      <c r="AK66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6145,8 +6465,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6246,8 +6568,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6347,8 +6675,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6448,8 +6782,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6549,38 +6889,44 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12993100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>13997300</v>
+      </c>
+      <c r="F72" s="3">
         <v>7786300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>7840100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>16771300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>16059500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>9257600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>9213400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>15052900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>5</v>
       </c>
@@ -6608,50 +6954,56 @@
       <c r="U72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>38341200</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>35396700</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>34086400</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>29060800</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3">
         <v>28350400</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="3">
         <v>25598200</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>25760400</v>
       </c>
-      <c r="AI72" s="3" t="s">
+      <c r="AK72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6751,8 +7103,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6852,8 +7210,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6953,38 +7317,44 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>69900600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>75303400</v>
+      </c>
+      <c r="F76" s="3">
         <v>69436400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>69915800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>67444500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>64581900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>63009800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>62708600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>58898200</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>5</v>
       </c>
@@ -7012,50 +7382,56 @@
       <c r="U76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V76" s="3">
+      <c r="V76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="3">
         <v>42710900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z76" s="3">
         <v>39618800</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="3">
         <v>38199400</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD76" s="3">
         <v>32929000</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF76" s="3">
         <v>32502900</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH76" s="3">
         <v>30113100</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>30980400</v>
       </c>
-      <c r="AI76" s="3" t="s">
+      <c r="AK76" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7155,114 +7531,126 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7290,80 +7678,86 @@
       <c r="K81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>7107500</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3">
         <v>7314400</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>5607400</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>4169100</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>569500</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>4556400</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>3844500</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="3">
         <v>3962700</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD81" s="3">
         <v>3298400</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF81" s="3">
         <v>3633000</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH81" s="3">
         <v>2386500</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>2664500</v>
       </c>
-      <c r="AI81" s="3" t="s">
+      <c r="AK81" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7399,109 +7793,117 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1318100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1262200</v>
+      </c>
+      <c r="F83" s="3">
         <v>1566600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1559100</v>
       </c>
-      <c r="F83" s="3">
-        <v>1225800</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
+        <v>1216200</v>
+      </c>
+      <c r="I83" s="3">
         <v>1124700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1447300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1538000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>780200</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>6320300</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>6034300</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>3203400</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>2781000</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>1462100</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>1170500</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF83" s="3">
         <v>1532600</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH83" s="3">
         <v>1133200</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>1526000</v>
       </c>
-      <c r="AI83" s="3" t="s">
+      <c r="AK83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7601,8 +8003,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7702,8 +8110,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7803,8 +8217,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7904,8 +8324,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8005,109 +8431,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6025500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>6491200</v>
+      </c>
+      <c r="F89" s="3">
         <v>3902300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>3929200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>6438600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>6165300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>3684500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>3666900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>5646600</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
         <v>20216300</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>10868700</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>8707700</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>4927900</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>6303700</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>3470800</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>5345200</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH89" s="3">
         <v>2542400</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>5407700</v>
       </c>
-      <c r="AI89" s="3" t="s">
+      <c r="AK89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8143,109 +8581,117 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1028600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1108100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1461500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1471600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1792300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1716200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1945400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1936100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1343900</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1197000</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1978800</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-2034800</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-1314000</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-1961200</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-1038700</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-1257800</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-861700</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-1928600</v>
       </c>
-      <c r="AI91" s="3" t="s">
+      <c r="AK91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8345,8 +8791,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8446,109 +8898,121 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1747100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1882100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1695100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1706800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-2329500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-2230600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-2235300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2224600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2071200</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-17322800</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-2931400</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-2896300</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-3985600</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-2602400</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-1360400</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-8053600</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-1603300</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-1367500</v>
       </c>
-      <c r="AI94" s="3" t="s">
+      <c r="AK94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8584,109 +9048,117 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1421000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1530800</v>
+      </c>
+      <c r="F96" s="3">
         <v>2007400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>2021300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>1518700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>1454300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>1912100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>1903000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>1338600</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-4510900</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-2427700</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-1367000</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-2837500</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1190000</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1876500</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-902100</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-1465300</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-826400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8786,8 +9258,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8887,8 +9365,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8988,307 +9472,331 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2987400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-3218300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2649200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-2667500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2976100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2849800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2190000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2179500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-3660900</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>-16430600</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>7383800</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>-3917800</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-1621100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-3320400</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-1664600</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-2373000</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH100" s="3">
         <v>4794300</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-3366500</v>
       </c>
-      <c r="AI100" s="3" t="s">
+      <c r="AK100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-127700</v>
+        <v>-21600</v>
       </c>
       <c r="E101" s="3">
-        <v>-127100</v>
+        <v>-20600</v>
       </c>
       <c r="F101" s="3">
         <v>-127700</v>
       </c>
       <c r="G101" s="3">
+        <v>-127100</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-127700</v>
+      </c>
+      <c r="I101" s="3">
         <v>-117200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>153700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>163300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>212100</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>539900</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>-1049300</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>28000</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>17600</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="3">
         <v>45000</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
         <v>31800</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-30300</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-97600</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI101" s="3" t="s">
+      <c r="AK101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1323100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1425400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-432300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-435300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1111400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1064200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-868400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-864300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-213200</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
         <v>-12997300</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>14271800</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>1921600</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-661100</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>425800</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>477600</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-5270000</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="3">
         <v>5585300</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>672600</v>
       </c>
-      <c r="AI102" s="3" t="s">
+      <c r="AK102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="92">
   <si>
     <t>LVMUY</t>
   </si>
@@ -656,155 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -835,83 +841,89 @@
       <c r="L8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O8" s="3">
         <v>21349200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>39964800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>19533300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>38539800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>16704900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>30327600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>14249300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>26189700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>12408100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>20065100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>11963900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>33373900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>16312000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>29506500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>14998000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>29662400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>12603400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>23881500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>12178100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>25718300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>11647400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>22118900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>11601900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>23959800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>10726300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -945,80 +957,86 @@
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>12423900</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>12191800</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>9635200</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>8845900</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>7638600</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>11295900</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="3">
         <v>9937100</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="3">
         <v>10048700</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="3">
         <v>7828700</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH9" s="3">
         <v>8866000</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>7720400</v>
       </c>
-      <c r="AI9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL9" s="3">
         <v>8359900</v>
       </c>
-      <c r="AK9" s="3" t="s">
+      <c r="AM9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1052,80 +1070,86 @@
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>27540900</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>26348000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>20692400</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>17343800</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>12426600</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>22078100</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="3">
         <v>19569400</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="3">
         <v>19613700</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="3">
         <v>16052800</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="3">
         <v>16852300</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>14398500</v>
       </c>
-      <c r="AI10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="3">
         <v>15599900</v>
       </c>
-      <c r="AK10" s="3" t="s">
+      <c r="AM10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1163,8 +1187,10 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1270,8 +1296,14 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1377,8 +1409,14 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1412,80 +1450,86 @@
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>117500</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>94300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>32800</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>150600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>136400</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>101600</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="3">
         <v>48200</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
         <v>62700</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF14" s="3">
         <v>80200</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH14" s="3">
         <v>150300</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>111100</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL14" s="3">
         <v>159600</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AM14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1516,11 +1560,11 @@
       <c r="L15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1582,17 +1626,23 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-      <c r="AI15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ15" s="3" t="s">
-        <v>5</v>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
       </c>
       <c r="AK15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1627,8 +1677,10 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1662,80 +1714,86 @@
       <c r="M17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3">
         <v>28945600</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>28179000</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>22300500</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>19751500</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>18410200</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>26332100</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="3">
         <v>23341000</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="3">
         <v>23394200</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="3">
         <v>18854900</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH17" s="3">
         <v>20593000</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>18141500</v>
       </c>
-      <c r="AI17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL17" s="3">
         <v>19282200</v>
       </c>
-      <c r="AK17" s="3" t="s">
+      <c r="AM17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1769,80 +1827,86 @@
       <c r="M18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <v>11019200</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>10360700</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>8027000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>6438200</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>1654900</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>7041800</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>6165500</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>6268200</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF18" s="3">
         <v>5026600</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH18" s="3">
         <v>5125300</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>3977500</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL18" s="3">
         <v>4677600</v>
       </c>
-      <c r="AK18" s="3" t="s">
+      <c r="AM18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1880,8 +1944,10 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1915,80 +1981,86 @@
       <c r="M20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-725800</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>181000</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>153400</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>4000</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>-268400</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-151800</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>20000</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-332400</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF20" s="3">
         <v>56000</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH20" s="3">
         <v>57200</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>66200</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-248800</v>
       </c>
-      <c r="AK20" s="3" t="s">
+      <c r="AM20" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2028,74 +2100,80 @@
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>16862100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>12476500</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>10093400</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>8966500</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>7397900</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>6253100</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>6715100</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>5176900</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL21" s="3">
         <v>5954700</v>
       </c>
-      <c r="AK21" s="3" t="s">
+      <c r="AM21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2129,80 +2207,86 @@
       <c r="M22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3">
         <v>142500</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3">
         <v>110600</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>140700</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>149600</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>235600</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="3">
         <v>261500</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB22" s="3">
         <v>261200</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="3">
         <v>100500</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF22" s="3">
         <v>80200</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH22" s="3">
         <v>102100</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>87500</v>
       </c>
-      <c r="AI22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL22" s="3">
         <v>63400</v>
       </c>
-      <c r="AK22" s="3" t="s">
+      <c r="AM22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2236,80 +2320,86 @@
       <c r="M23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3">
         <v>10150900</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>10431200</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>8039700</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>6292600</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>1150900</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>6628600</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB23" s="3">
         <v>5924400</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="3">
         <v>5835200</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF23" s="3">
         <v>5002500</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH23" s="3">
         <v>5080400</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>3956100</v>
       </c>
-      <c r="AI23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL23" s="3">
         <v>4365400</v>
       </c>
-      <c r="AK23" s="3" t="s">
+      <c r="AM23" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2343,80 +2433,86 @@
       <c r="M24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3">
         <v>2595100</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>2710300</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>2128700</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>1893100</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>557500</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3">
         <v>1752300</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB24" s="3">
         <v>1683400</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD24" s="3">
         <v>1460900</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF24" s="3">
         <v>1387900</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH24" s="3">
         <v>1154500</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>1329600</v>
       </c>
-      <c r="AI24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL24" s="3">
         <v>1430900</v>
       </c>
-      <c r="AK24" s="3" t="s">
+      <c r="AM24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2522,8 +2618,14 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2557,80 +2659,86 @@
       <c r="M26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3">
         <v>7555800</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>7721000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>5911000</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>4399500</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>593500</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>4876300</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="3">
         <v>4240900</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD26" s="3">
         <v>4374400</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF26" s="3">
         <v>3614600</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH26" s="3">
         <v>3925800</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>2626600</v>
       </c>
-      <c r="AI26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL26" s="3">
         <v>2934500</v>
       </c>
-      <c r="AK26" s="3" t="s">
+      <c r="AM26" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2664,80 +2772,86 @@
       <c r="M27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3">
         <v>7107500</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>7314400</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>5607400</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>4169100</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>569500</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>4556400</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="3">
         <v>3844500</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD27" s="3">
         <v>3962700</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF27" s="3">
         <v>3298400</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH27" s="3">
         <v>3633000</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>2386500</v>
       </c>
-      <c r="AI27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL27" s="3">
         <v>2664500</v>
       </c>
-      <c r="AK27" s="3" t="s">
+      <c r="AM27" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2843,8 +2957,14 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2875,11 +2995,11 @@
       <c r="L29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2950,8 +3070,14 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3057,8 +3183,14 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3164,8 +3296,14 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3199,80 +3337,86 @@
       <c r="M32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>725800</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>-181000</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>-153400</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>-4000</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>268400</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>151800</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>332400</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-57200</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-66200</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL32" s="3">
         <v>248800</v>
       </c>
-      <c r="AK32" s="3" t="s">
+      <c r="AM32" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3306,80 +3450,86 @@
       <c r="M33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3">
         <v>7107500</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>7314400</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>5607400</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>4169100</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>569500</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>4556400</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB33" s="3">
         <v>3844500</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD33" s="3">
         <v>3962700</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF33" s="3">
         <v>3298400</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH33" s="3">
         <v>3633000</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>2386500</v>
       </c>
-      <c r="AI33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL33" s="3">
         <v>2664500</v>
       </c>
-      <c r="AK33" s="3" t="s">
+      <c r="AM33" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3485,8 +3635,14 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3520,192 +3676,204 @@
       <c r="M35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3">
         <v>7107500</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>7314400</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>5607400</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>4169100</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>569500</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>4556400</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="3">
         <v>3844500</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD35" s="3">
         <v>3962700</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF35" s="3">
         <v>3298400</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH35" s="3">
         <v>3633000</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>2386500</v>
       </c>
-      <c r="AI35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL35" s="3">
         <v>2664500</v>
       </c>
-      <c r="AK35" s="3" t="s">
+      <c r="AM35" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3743,8 +3911,10 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3782,44 +3952,46 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9601900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8837000</v>
+      </c>
+      <c r="F41" s="3">
         <v>9971000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>10741700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>7666300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>7719300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>8592900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8228200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>6708500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>6676400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7801600</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>5</v>
       </c>
@@ -3847,86 +4019,92 @@
       <c r="W41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X41" s="3">
+      <c r="X41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z41" s="3">
         <v>6622700</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3">
         <v>4704400</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" s="3">
         <v>5453200</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF41" s="3">
         <v>4635800</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH41" s="3">
         <v>4194000</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>9479700</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL41" s="3">
         <v>4160000</v>
       </c>
-      <c r="AK41" s="3" t="s">
+      <c r="AM41" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4880800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>4492000</v>
+      </c>
+      <c r="F42" s="3">
         <v>4118400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>4436800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>4223700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>4252900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>3884200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>3719300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>4625500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>4603400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>3830300</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>5</v>
       </c>
@@ -3954,86 +4132,92 @@
       <c r="W42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X42" s="3">
+      <c r="X42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z42" s="3">
         <v>855700</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB42" s="3">
         <v>927000</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="3">
         <v>787800</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="3">
         <v>799300</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH42" s="3">
         <v>577800</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>572200</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL42" s="3">
         <v>439000</v>
       </c>
-      <c r="AK42" s="3" t="s">
+      <c r="AM42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8758700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>8061000</v>
+      </c>
+      <c r="F43" s="3">
         <v>9085800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>9788100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>8540700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>8599600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>8780800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>8408100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>7742400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>7705300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>7598600</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
@@ -4061,86 +4245,92 @@
       <c r="W43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X43" s="3">
+      <c r="X43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z43" s="3">
         <v>6420800</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3">
         <v>5759700</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
         <v>5939300</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF43" s="3">
         <v>4967400</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH43" s="3">
         <v>5413600</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>4061600</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL43" s="3">
         <v>4816100</v>
       </c>
-      <c r="AK43" s="3" t="s">
+      <c r="AM43" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>27116900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>24956800</v>
+      </c>
+      <c r="F44" s="3">
         <v>24504600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>26398600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>26031300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>26211000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>25369700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>24293000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>24714000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>24595800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>21715300</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
@@ -4168,86 +4358,92 @@
       <c r="W44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X44" s="3">
+      <c r="X44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="3">
         <v>16013400</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="3">
         <v>15953200</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD44" s="3">
         <v>14768500</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF44" s="3">
         <v>13047500</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH44" s="3">
         <v>12216200</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>12190400</v>
       </c>
-      <c r="AI44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL44" s="3">
         <v>12379000</v>
       </c>
-      <c r="AK44" s="3" t="s">
+      <c r="AM44" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1361100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1252700</v>
+      </c>
+      <c r="F45" s="3">
         <v>598400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>644700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>807900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>813500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>934000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>894400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1288200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1282100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>869900</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
@@ -4275,86 +4471,92 @@
       <c r="W45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z45" s="3">
         <v>1035500</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB45" s="3">
         <v>1014100</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD45" s="3">
         <v>909700</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF45" s="3">
         <v>888300</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH45" s="3">
         <v>1228600</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>1173600</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL45" s="3">
         <v>975400</v>
       </c>
-      <c r="AK45" s="3" t="s">
+      <c r="AM45" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>52729300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>48529000</v>
+      </c>
+      <c r="F46" s="3">
         <v>49146900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>52945600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>48134600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>48466900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>48314400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>46263800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>45853700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>45634500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>42470900</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>5</v>
       </c>
@@ -4382,86 +4584,92 @@
       <c r="W46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X46" s="3">
+      <c r="X46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z46" s="3">
         <v>30948000</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB46" s="3">
         <v>28358300</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD46" s="3">
         <v>27858500</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF46" s="3">
         <v>24338300</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH46" s="3">
         <v>23630200</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>27477500</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL46" s="3">
         <v>22769600</v>
       </c>
-      <c r="AK46" s="3" t="s">
+      <c r="AM46" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3409300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3137700</v>
+      </c>
+      <c r="F47" s="3">
         <v>3084200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>3322600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>2715100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>2733800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2604200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2493600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2699800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2686900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2324500</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4489,86 +4697,92 @@
       <c r="W47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X47" s="3">
+      <c r="X47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
         <v>3162500</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3">
         <v>2750400</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
         <v>2862600</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF47" s="3">
         <v>2390300</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH47" s="3">
         <v>2257400</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>2228300</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL47" s="3">
         <v>2461500</v>
       </c>
-      <c r="AK47" s="3" t="s">
+      <c r="AM47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>52997100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>48775400</v>
+      </c>
+      <c r="F48" s="3">
         <v>48147800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>51869300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>47777800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>48107700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>47540600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>45522900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>43245600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>43038900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>40258600</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4596,86 +4810,92 @@
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X48" s="3">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>35699400</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>32928600</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>17876000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>15549900</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" s="3">
         <v>30370000</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>27241900</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL48" s="3">
         <v>14248900</v>
       </c>
-      <c r="AK48" s="3" t="s">
+      <c r="AM48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>50978300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>46917400</v>
+      </c>
+      <c r="F49" s="3">
         <v>48231700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>51959600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>50652500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>51002300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>54837000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>52509500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>55044800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>54781600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>53664600</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4703,50 +4923,56 @@
       <c r="W49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X49" s="3">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z49" s="3">
         <v>39234300</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3">
         <v>39610600</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD49" s="3">
         <v>36647400</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF49" s="3">
         <v>34095100</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH49" s="3">
         <v>68466100</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>56139900</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL49" s="3">
         <v>27861600</v>
       </c>
-      <c r="AK49" s="3" t="s">
+      <c r="AM49" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4852,8 +5078,14 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4959,44 +5191,50 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1052300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>968400</v>
+      </c>
+      <c r="F52" s="3">
         <v>860300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>926800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>851800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>857700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>853300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>817100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>845000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>840900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>793000</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
@@ -5024,50 +5262,56 @@
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>3619000</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>3315100</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>2645000</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>2396900</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3">
         <v>2273200</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>2462800</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL52" s="3">
         <v>2643400</v>
       </c>
-      <c r="AK52" s="3" t="s">
+      <c r="AM52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5173,44 +5417,50 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>166265400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>153021000</v>
+      </c>
+      <c r="F54" s="3">
         <v>154457000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>166395300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>154772300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>155841000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>158830600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>152089300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>152156100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>151428700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>143898700</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>5</v>
       </c>
@@ -5238,50 +5488,56 @@
       <c r="W54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X54" s="3">
+      <c r="X54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="3">
         <v>112663200</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="3">
         <v>106963000</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD54" s="3">
         <v>87889500</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF54" s="3">
         <v>78770500</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH54" s="3">
         <v>78264400</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>73859500</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL54" s="3">
         <v>69984900</v>
       </c>
-      <c r="AK54" s="3" t="s">
+      <c r="AM54" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5319,8 +5575,10 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5358,44 +5616,46 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9085100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>8361400</v>
+      </c>
+      <c r="F57" s="3">
         <v>8934700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>9625300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>8796700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>8857500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>10002200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>9577700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>8978200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>8935200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>9391900</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5423,86 +5683,92 @@
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>6787300</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>6073800</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>6285900</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3">
         <v>5059600</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="3">
         <v>5092700</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>4320800</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL57" s="3">
         <v>4911200</v>
       </c>
-      <c r="AK57" s="3" t="s">
+      <c r="AM57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>15345900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>14123400</v>
+      </c>
+      <c r="F58" s="3">
         <v>14770700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>15912300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>16050600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>16161400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>15320000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>14669800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>17861400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>17776000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>13178400</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>5</v>
       </c>
@@ -5530,86 +5796,92 @@
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X58" s="3">
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>11395100</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>11668700</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>5924000</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="3">
         <v>6213600</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH58" s="3">
         <v>5487700</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>5463000</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL58" s="3">
         <v>4013300</v>
       </c>
-      <c r="AK58" s="3" t="s">
+      <c r="AM58" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7074600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6511000</v>
+      </c>
+      <c r="F59" s="3">
         <v>6308100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>6795700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>6018400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>6060000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>6453000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>6179100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>6852600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>6819900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>6874000</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5637,86 +5909,92 @@
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X59" s="3">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>8227900</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3">
         <v>7018400</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>7701900</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF59" s="3">
         <v>6037900</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH59" s="3">
         <v>6679200</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>5213900</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL59" s="3">
         <v>6112000</v>
       </c>
-      <c r="AK59" s="3" t="s">
+      <c r="AM59" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35745200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>32897800</v>
+      </c>
+      <c r="F60" s="3">
         <v>34885600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>37582000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>34849500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>35090100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>36636500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>35081500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>37434500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>37255500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>33710600</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>5</v>
       </c>
@@ -5744,86 +6022,92 @@
       <c r="W60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X60" s="3">
+      <c r="X60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z60" s="3">
         <v>26410300</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB60" s="3">
         <v>24760900</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD60" s="3">
         <v>19911800</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF60" s="3">
         <v>17311100</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH60" s="3">
         <v>16817500</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>14997600</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL60" s="3">
         <v>15036500</v>
       </c>
-      <c r="AK60" s="3" t="s">
+      <c r="AM60" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>31283600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>28791600</v>
+      </c>
+      <c r="F61" s="3">
         <v>27991500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>30155000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>27719900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>27911300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>27784900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>26605600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>24015300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>23900500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>24917200</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -5852,85 +6136,91 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>18064500</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>18501200</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>7103300</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>7347800</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>7905500</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>9213800</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
         <v>4615400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11517300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>10599900</v>
+      </c>
+      <c r="F62" s="3">
         <v>11570600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>12464900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>12634700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>12722000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>16679600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>15971600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>17234700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>17152300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>16682700</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>5</v>
       </c>
@@ -5958,50 +6248,56 @@
       <c r="W62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X62" s="3">
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3">
         <v>23400700</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3">
         <v>22068100</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>20706700</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="3">
         <v>19544400</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH62" s="3">
         <v>19458700</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>17915900</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL62" s="3">
         <v>17580200</v>
       </c>
-      <c r="AK62" s="3" t="s">
+      <c r="AM62" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6107,8 +6403,14 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6214,8 +6516,14 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6321,44 +6629,50 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>87727500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>80739300</v>
+      </c>
+      <c r="F66" s="3">
         <v>82723900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>89117800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>83541200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>84118000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>89524700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>85725000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>87255500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>86838300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>83404900</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>5</v>
       </c>
@@ -6386,50 +6700,56 @@
       <c r="W66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X66" s="3">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3">
         <v>69952400</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3">
         <v>67344200</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3">
         <v>49690100</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF66" s="3">
         <v>45841500</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH66" s="3">
         <v>45761500</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>43746400</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL66" s="3">
         <v>39004500</v>
       </c>
-      <c r="AK66" s="3" t="s">
+      <c r="AM66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6467,8 +6787,10 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6574,8 +6896,14 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6681,8 +7009,14 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6788,8 +7122,14 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6895,44 +7235,50 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6691700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>6158700</v>
+      </c>
+      <c r="F72" s="3">
         <v>12993100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>13997300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>7786300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>7840100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>16771300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>16059500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>9257600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>9213400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>15052900</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>5</v>
       </c>
@@ -6960,50 +7306,56 @@
       <c r="W72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>38341200</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>35396700</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>34086400</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3">
         <v>29060800</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="3">
         <v>28350400</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>25598200</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL72" s="3">
         <v>25760400</v>
       </c>
-      <c r="AK72" s="3" t="s">
+      <c r="AM72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7109,8 +7461,14 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7216,8 +7574,14 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7323,44 +7687,50 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>76682300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>70573900</v>
+      </c>
+      <c r="F76" s="3">
         <v>69900600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>75303400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>69436400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>69915800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>67444500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>64581900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>63009800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>62708600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>58898200</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>5</v>
       </c>
@@ -7388,50 +7758,56 @@
       <c r="W76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X76" s="3">
+      <c r="X76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z76" s="3">
         <v>42710900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="3">
         <v>39618800</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD76" s="3">
         <v>38199400</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF76" s="3">
         <v>32929000</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH76" s="3">
         <v>32502900</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>30113100</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL76" s="3">
         <v>30980400</v>
       </c>
-      <c r="AK76" s="3" t="s">
+      <c r="AM76" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7537,120 +7913,132 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7684,80 +8072,86 @@
       <c r="M81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3">
         <v>7107500</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>7314400</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>5607400</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>4169100</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>569500</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>4556400</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="3">
         <v>3844500</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD81" s="3">
         <v>3962700</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF81" s="3">
         <v>3298400</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH81" s="3">
         <v>3633000</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>2386500</v>
       </c>
-      <c r="AI81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL81" s="3">
         <v>2664500</v>
       </c>
-      <c r="AK81" s="3" t="s">
+      <c r="AM81" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7795,115 +8189,123 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1681100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1692700</v>
+      </c>
+      <c r="F83" s="3">
         <v>1318100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1262200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1566600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1559100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1216200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1124700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1447300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1538000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>780200</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>6320300</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>6034300</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>3203400</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>2781000</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>1462100</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF83" s="3">
         <v>1170500</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH83" s="3">
         <v>1532600</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>1133200</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL83" s="3">
         <v>1526000</v>
       </c>
-      <c r="AK83" s="3" t="s">
+      <c r="AM83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8009,8 +8411,14 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8116,8 +8524,14 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8223,8 +8637,14 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8330,8 +8750,14 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8437,115 +8863,127 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4627700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>4259100</v>
+      </c>
+      <c r="F89" s="3">
         <v>6025500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>6491200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>3902300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>3929200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>6438600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>6165300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>3684500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>3666900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>5646600</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>20216300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>10868700</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>8707700</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>4927900</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>6303700</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>3470800</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH89" s="3">
         <v>5345200</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>2542400</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL89" s="3">
         <v>5407700</v>
       </c>
-      <c r="AK89" s="3" t="s">
+      <c r="AM89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8583,115 +9021,123 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1385800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1275400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1028600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1108100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1461500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1471600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1792300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1716200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1945400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1936100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1343900</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1197000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V91" s="3">
         <v>-1978800</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-2034800</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-1314000</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-1961200</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-1038700</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-1257800</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-861700</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-1928600</v>
       </c>
-      <c r="AK91" s="3" t="s">
+      <c r="AM91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8797,8 +9243,14 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8904,115 +9356,127 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1439800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1325100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1747100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1882100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1695100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1706800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-2329500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2230600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2235300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2224600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-2071200</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-17322800</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-2931400</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-2896300</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-3985600</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-2602400</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-1360400</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-8053600</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-1603300</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-1367500</v>
       </c>
-      <c r="AK94" s="3" t="s">
+      <c r="AM94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9050,115 +9514,123 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2192600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>2017900</v>
+      </c>
+      <c r="F96" s="3">
         <v>1421000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>1530800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>2007400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>2021300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>1518700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>1454300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>1912100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>1903000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>1338600</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-4510900</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-2427700</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1367000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-2837500</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1190000</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1876500</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-902100</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-1465300</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-826400</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9264,8 +9736,14 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9371,8 +9849,14 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9478,325 +9962,349 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3973600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-3657000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2987400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-3218300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2649200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2667500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2976100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2849800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2190000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2179500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-3660900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>-16430600</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>7383800</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-3917800</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-1621100</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-3320400</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-1664600</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-2373000</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>4794300</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-3366500</v>
       </c>
-      <c r="AK100" s="3" t="s">
+      <c r="AM100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F101" s="3">
         <v>-21600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-20600</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-127700</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-127100</v>
       </c>
       <c r="H101" s="3">
         <v>-127700</v>
       </c>
       <c r="I101" s="3">
+        <v>-127100</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-127700</v>
+      </c>
+      <c r="K101" s="3">
         <v>-117200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>153700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>163300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>212100</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>539900</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>-1049300</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>28000</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="3">
         <v>17600</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
         <v>45000</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF101" s="3">
         <v>31800</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-30300</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-97600</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK101" s="3" t="s">
+      <c r="AM101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-854400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-786300</v>
+      </c>
+      <c r="F102" s="3">
         <v>1323100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1425400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-432300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-435300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1111400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1064200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-868400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-864300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-213200</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>-12997300</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>14271800</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>1921600</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-661100</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>425800</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>477600</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-5270000</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>5585300</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL102" s="3">
         <v>672600</v>
       </c>
-      <c r="AK102" s="3" t="s">
+      <c r="AM102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="92">
   <si>
     <t>LVMUY</t>
   </si>
@@ -656,161 +656,167 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -847,83 +853,89 @@
       <c r="N8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="3">
         <v>21349200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>39964800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>19533300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>38539800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>16704900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>30327600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>14249300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>26189700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>12408100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>20065100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>11963900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>33373900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>16312000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>29506500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>14998000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>29662400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>12603400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>23881500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>12178100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>25718300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>11647400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>22118900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>11601900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>23959800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>10726300</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -963,80 +975,86 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>12423900</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>12191800</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>9635200</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>8845900</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>7638600</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="3">
         <v>11295900</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="3">
         <v>9937100</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="3">
         <v>10048700</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH9" s="3">
         <v>7828700</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>8866000</v>
       </c>
-      <c r="AI9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL9" s="3">
         <v>7720400</v>
       </c>
-      <c r="AK9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN9" s="3">
         <v>8359900</v>
       </c>
-      <c r="AM9" s="3" t="s">
+      <c r="AO9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1076,80 +1094,86 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>27540900</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>26348000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>20692400</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>17343800</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>12426600</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="3">
         <v>22078100</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="3">
         <v>19569400</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="3">
         <v>19613700</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="3">
         <v>16052800</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>16852300</v>
       </c>
-      <c r="AI10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="3">
         <v>14398500</v>
       </c>
-      <c r="AK10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN10" s="3">
         <v>15599900</v>
       </c>
-      <c r="AM10" s="3" t="s">
+      <c r="AO10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1189,8 +1213,10 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1302,8 +1328,14 @@
       <c r="AM12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1415,8 +1447,14 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1456,80 +1494,86 @@
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>117500</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>94300</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>32800</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>150600</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>136400</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="3">
         <v>101600</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
         <v>48200</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF14" s="3">
         <v>62700</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH14" s="3">
         <v>80200</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>150300</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL14" s="3">
         <v>111100</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN14" s="3">
         <v>159600</v>
       </c>
-      <c r="AM14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1566,11 +1610,11 @@
       <c r="N15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1632,17 +1676,23 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
-      <c r="AK15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL15" s="3" t="s">
-        <v>5</v>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>0</v>
       </c>
       <c r="AM15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1679,8 +1729,10 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1720,80 +1772,86 @@
       <c r="O17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>28945600</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>28179000</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>22300500</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>19751500</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>18410200</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="3">
         <v>26332100</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="3">
         <v>23341000</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="3">
         <v>23394200</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH17" s="3">
         <v>18854900</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>20593000</v>
       </c>
-      <c r="AI17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL17" s="3">
         <v>18141500</v>
       </c>
-      <c r="AK17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN17" s="3">
         <v>19282200</v>
       </c>
-      <c r="AM17" s="3" t="s">
+      <c r="AO17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1833,80 +1891,86 @@
       <c r="O18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>11019200</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>10360700</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>8027000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>6438200</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>1654900</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>7041800</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>6165500</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF18" s="3">
         <v>6268200</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH18" s="3">
         <v>5026600</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>5125300</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL18" s="3">
         <v>3977500</v>
       </c>
-      <c r="AK18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN18" s="3">
         <v>4677600</v>
       </c>
-      <c r="AM18" s="3" t="s">
+      <c r="AO18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1946,8 +2010,10 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1987,80 +2053,86 @@
       <c r="O20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-725800</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>181000</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>153400</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>4000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-268400</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-151800</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>20000</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-332400</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH20" s="3">
         <v>56000</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>57200</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL20" s="3">
         <v>66200</v>
       </c>
-      <c r="AK20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN20" s="3">
         <v>-248800</v>
       </c>
-      <c r="AM20" s="3" t="s">
+      <c r="AO20" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2106,74 +2178,80 @@
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>16862100</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>12476500</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>10093400</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>8966500</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>7397900</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>6253100</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>6715100</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL21" s="3">
         <v>5176900</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN21" s="3">
         <v>5954700</v>
       </c>
-      <c r="AM21" s="3" t="s">
+      <c r="AO21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2213,80 +2291,86 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3">
         <v>142500</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>110600</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>140700</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>149600</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="3">
         <v>235600</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB22" s="3">
         <v>261500</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="3">
         <v>261200</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF22" s="3">
         <v>100500</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH22" s="3">
         <v>80200</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>102100</v>
       </c>
-      <c r="AI22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL22" s="3">
         <v>87500</v>
       </c>
-      <c r="AK22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN22" s="3">
         <v>63400</v>
       </c>
-      <c r="AM22" s="3" t="s">
+      <c r="AO22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2326,80 +2410,86 @@
       <c r="O23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>10150900</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>10431200</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>8039700</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>6292600</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>1150900</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB23" s="3">
         <v>6628600</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="3">
         <v>5924400</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF23" s="3">
         <v>5835200</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH23" s="3">
         <v>5002500</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>5080400</v>
       </c>
-      <c r="AI23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL23" s="3">
         <v>3956100</v>
       </c>
-      <c r="AK23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN23" s="3">
         <v>4365400</v>
       </c>
-      <c r="AM23" s="3" t="s">
+      <c r="AO23" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2439,80 +2529,86 @@
       <c r="O24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>2595100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>2710300</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>2128700</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>1893100</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3">
         <v>557500</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB24" s="3">
         <v>1752300</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD24" s="3">
         <v>1683400</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF24" s="3">
         <v>1460900</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH24" s="3">
         <v>1387900</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>1154500</v>
       </c>
-      <c r="AI24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL24" s="3">
         <v>1329600</v>
       </c>
-      <c r="AK24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN24" s="3">
         <v>1430900</v>
       </c>
-      <c r="AM24" s="3" t="s">
+      <c r="AO24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2624,8 +2720,14 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2665,80 +2767,86 @@
       <c r="O26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>7555800</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>7721000</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>5911000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>4399500</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>593500</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="3">
         <v>4876300</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD26" s="3">
         <v>4240900</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF26" s="3">
         <v>4374400</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH26" s="3">
         <v>3614600</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>3925800</v>
       </c>
-      <c r="AI26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL26" s="3">
         <v>2626600</v>
       </c>
-      <c r="AK26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN26" s="3">
         <v>2934500</v>
       </c>
-      <c r="AM26" s="3" t="s">
+      <c r="AO26" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2778,80 +2886,86 @@
       <c r="O27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>7107500</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>7314400</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>5607400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>4169100</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>569500</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="3">
         <v>4556400</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD27" s="3">
         <v>3844500</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF27" s="3">
         <v>3962700</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH27" s="3">
         <v>3298400</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>3633000</v>
       </c>
-      <c r="AI27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL27" s="3">
         <v>2386500</v>
       </c>
-      <c r="AK27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN27" s="3">
         <v>2664500</v>
       </c>
-      <c r="AM27" s="3" t="s">
+      <c r="AO27" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2963,8 +3077,14 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3001,11 +3121,11 @@
       <c r="N29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -3076,8 +3196,14 @@
       <c r="AM29" s="3">
         <v>0</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3189,8 +3315,14 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3302,8 +3434,14 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3343,80 +3481,86 @@
       <c r="O32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>725800</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>-181000</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>-153400</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>-4000</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>268400</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>151800</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF32" s="3">
         <v>332400</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-57200</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-66200</v>
       </c>
-      <c r="AK32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN32" s="3">
         <v>248800</v>
       </c>
-      <c r="AM32" s="3" t="s">
+      <c r="AO32" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3456,80 +3600,86 @@
       <c r="O33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>7107500</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>7314400</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>5607400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>4169100</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>569500</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB33" s="3">
         <v>4556400</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD33" s="3">
         <v>3844500</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF33" s="3">
         <v>3962700</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH33" s="3">
         <v>3298400</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>3633000</v>
       </c>
-      <c r="AI33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL33" s="3">
         <v>2386500</v>
       </c>
-      <c r="AK33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN33" s="3">
         <v>2664500</v>
       </c>
-      <c r="AM33" s="3" t="s">
+      <c r="AO33" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3641,8 +3791,14 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3682,198 +3838,210 @@
       <c r="O35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>7107500</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>7314400</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>5607400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>4169100</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>569500</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="3">
         <v>4556400</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD35" s="3">
         <v>3844500</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF35" s="3">
         <v>3962700</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH35" s="3">
         <v>3298400</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>3633000</v>
       </c>
-      <c r="AI35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL35" s="3">
         <v>2386500</v>
       </c>
-      <c r="AK35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN35" s="3">
         <v>2664500</v>
       </c>
-      <c r="AM35" s="3" t="s">
+      <c r="AO35" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3913,8 +4081,10 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3954,50 +4124,52 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10325200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10318000</v>
+      </c>
+      <c r="F41" s="3">
         <v>9601900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8837000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9971000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>10741700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>7666300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7719300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8592900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8228200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>6708500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>6676400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>7801600</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>5</v>
       </c>
@@ -4025,92 +4197,98 @@
       <c r="Y41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3">
         <v>6622700</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" s="3">
         <v>4704400</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF41" s="3">
         <v>5453200</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH41" s="3">
         <v>4635800</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>4194000</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL41" s="3">
         <v>9479700</v>
       </c>
-      <c r="AK41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN41" s="3">
         <v>4160000</v>
       </c>
-      <c r="AM41" s="3" t="s">
+      <c r="AO41" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4880800</v>
+        <v>5548900</v>
       </c>
       <c r="E42" s="3">
-        <v>4492000</v>
+        <v>5545000</v>
       </c>
       <c r="F42" s="3">
+        <v>4897200</v>
+      </c>
+      <c r="G42" s="3">
+        <v>4507100</v>
+      </c>
+      <c r="H42" s="3">
         <v>4118400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>4436800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>4223700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>4252900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>3884200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>3719300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>4625500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>4603400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>3830300</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>5</v>
       </c>
@@ -4138,92 +4316,98 @@
       <c r="Y42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="Z42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB42" s="3">
         <v>855700</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="3">
         <v>927000</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="3">
         <v>787800</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH42" s="3">
         <v>799300</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>577800</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL42" s="3">
         <v>572200</v>
       </c>
-      <c r="AK42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN42" s="3">
         <v>439000</v>
       </c>
-      <c r="AM42" s="3" t="s">
+      <c r="AO42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8789500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>8783300</v>
+      </c>
+      <c r="F43" s="3">
         <v>8758700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>8061000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>9085800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>9788100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>8540700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>8599600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>8780800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>8408100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>7742400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>7705300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>7598600</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>5</v>
       </c>
@@ -4251,92 +4435,98 @@
       <c r="Y43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="Z43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3">
         <v>6420800</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
         <v>5759700</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF43" s="3">
         <v>5939300</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH43" s="3">
         <v>4967400</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>5413600</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL43" s="3">
         <v>4061600</v>
       </c>
-      <c r="AK43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN43" s="3">
         <v>4816100</v>
       </c>
-      <c r="AM43" s="3" t="s">
+      <c r="AO43" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>26604400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>26585700</v>
+      </c>
+      <c r="F44" s="3">
         <v>27116900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>24956800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>24504600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>26398600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>26031300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>26211000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>25369700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>24293000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>24714000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>24595800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>21715300</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>5</v>
       </c>
@@ -4364,92 +4554,98 @@
       <c r="Y44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="3">
         <v>16013400</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD44" s="3">
         <v>15953200</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF44" s="3">
         <v>14768500</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH44" s="3">
         <v>13047500</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>12216200</v>
       </c>
-      <c r="AI44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL44" s="3">
         <v>12190400</v>
       </c>
-      <c r="AK44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN44" s="3">
         <v>12379000</v>
       </c>
-      <c r="AM44" s="3" t="s">
+      <c r="AO44" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4446400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4443300</v>
+      </c>
+      <c r="F45" s="3">
         <v>1361100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1252700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>598400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>644700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>807900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>813500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>934000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>894400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1288200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1282100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>869900</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>5</v>
       </c>
@@ -4477,92 +4673,98 @@
       <c r="Y45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB45" s="3">
         <v>1035500</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD45" s="3">
         <v>1014100</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF45" s="3">
         <v>909700</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH45" s="3">
         <v>888300</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>1228600</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL45" s="3">
         <v>1173600</v>
       </c>
-      <c r="AK45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN45" s="3">
         <v>975400</v>
       </c>
-      <c r="AM45" s="3" t="s">
+      <c r="AO45" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>56568000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>56528200</v>
+      </c>
+      <c r="F46" s="3">
         <v>52729300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>48529000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>49146900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>52945600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>48134600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>48466900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>48314400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>46263800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>45853700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>45634500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>42470900</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>5</v>
       </c>
@@ -4590,92 +4792,98 @@
       <c r="Y46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="Z46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB46" s="3">
         <v>30948000</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD46" s="3">
         <v>28358300</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF46" s="3">
         <v>27858500</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH46" s="3">
         <v>24338300</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>23630200</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL46" s="3">
         <v>27477500</v>
       </c>
-      <c r="AK46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN46" s="3">
         <v>22769600</v>
       </c>
-      <c r="AM46" s="3" t="s">
+      <c r="AO46" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3649200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3646600</v>
+      </c>
+      <c r="F47" s="3">
         <v>3409300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>3137700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>3084200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>3322600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2715100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2733800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2604200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2493600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2699800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2686900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>2324500</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4703,92 +4911,98 @@
       <c r="Y47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3">
         <v>3162500</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
         <v>2750400</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF47" s="3">
         <v>2862600</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH47" s="3">
         <v>2390300</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>2257400</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL47" s="3">
         <v>2228300</v>
       </c>
-      <c r="AK47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN47" s="3">
         <v>2461500</v>
       </c>
-      <c r="AM47" s="3" t="s">
+      <c r="AO47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>52351800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>52314900</v>
+      </c>
+      <c r="F48" s="3">
         <v>52997100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>48775400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>48147800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>51869300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>47777800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>48107700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>47540600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>45522900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>43245600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>43038900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>40258600</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4816,92 +5030,98 @@
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>35699400</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>32928600</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>17876000</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" s="3">
         <v>15549900</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>30370000</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL48" s="3">
         <v>27241900</v>
       </c>
-      <c r="AK48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN48" s="3">
         <v>14248900</v>
       </c>
-      <c r="AM48" s="3" t="s">
+      <c r="AO48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>48660300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>48626100</v>
+      </c>
+      <c r="F49" s="3">
         <v>50978300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>46917400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>48231700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>51959600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>50652500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>51002300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>54837000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>52509500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>55044800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>54781600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>53664600</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4929,50 +5149,56 @@
       <c r="Y49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3">
         <v>39234300</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD49" s="3">
         <v>39610600</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF49" s="3">
         <v>36647400</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH49" s="3">
         <v>34095100</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>68466100</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL49" s="3">
         <v>56139900</v>
       </c>
-      <c r="AK49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN49" s="3">
         <v>27861600</v>
       </c>
-      <c r="AM49" s="3" t="s">
+      <c r="AO49" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5084,8 +5310,14 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5197,50 +5429,56 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>890000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>889400</v>
+      </c>
+      <c r="F52" s="3">
         <v>1052300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>968400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>860300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>926800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>851800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>857700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>853300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>817100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>845000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>840900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>793000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
@@ -5268,50 +5506,56 @@
       <c r="Y52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>3619000</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>3315100</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>2645000</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3">
         <v>2396900</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>2273200</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL52" s="3">
         <v>2462800</v>
       </c>
-      <c r="AK52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN52" s="3">
         <v>2643400</v>
       </c>
-      <c r="AM52" s="3" t="s">
+      <c r="AO52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5423,50 +5667,56 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>166768800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>166651400</v>
+      </c>
+      <c r="F54" s="3">
         <v>166265400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>153021000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>154457000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>166395300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>154772300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>155841000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>158830600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>152089300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>152156100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>151428700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>143898700</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>5</v>
       </c>
@@ -5494,50 +5744,56 @@
       <c r="Y54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="3">
         <v>112663200</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD54" s="3">
         <v>106963000</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF54" s="3">
         <v>87889500</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH54" s="3">
         <v>78770500</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>78264400</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL54" s="3">
         <v>73859500</v>
       </c>
-      <c r="AK54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN54" s="3">
         <v>69984900</v>
       </c>
-      <c r="AM54" s="3" t="s">
+      <c r="AO54" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5577,8 +5833,10 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5618,50 +5876,52 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9654800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>9648000</v>
+      </c>
+      <c r="F57" s="3">
         <v>9085100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>8361400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>8934700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>9625300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>8796700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>8857500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>10002200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>9577700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>8978200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>8935200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>9391900</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5689,92 +5949,98 @@
       <c r="Y57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>6787300</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>6073800</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3">
         <v>6285900</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="3">
         <v>5059600</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>5092700</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL57" s="3">
         <v>4320800</v>
       </c>
-      <c r="AK57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN57" s="3">
         <v>4911200</v>
       </c>
-      <c r="AM57" s="3" t="s">
+      <c r="AO57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12842600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>12833500</v>
+      </c>
+      <c r="F58" s="3">
         <v>15345900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>14123400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>14770700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>15912300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>16050600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>16161400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>15320000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>14669800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>17861400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>17776000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>13178400</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>5</v>
       </c>
@@ -5802,92 +6068,98 @@
       <c r="Y58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>11395100</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>11668700</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="3">
         <v>5924000</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH58" s="3">
         <v>6213600</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>5487700</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL58" s="3">
         <v>5463000</v>
       </c>
-      <c r="AK58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN58" s="3">
         <v>4013300</v>
       </c>
-      <c r="AM58" s="3" t="s">
+      <c r="AO58" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8238800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>8233000</v>
+      </c>
+      <c r="F59" s="3">
         <v>7074600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>6511000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>6308100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>6795700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>6018400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>6060000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>6453000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>6179100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>6852600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>6819900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>6874000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5915,92 +6187,98 @@
       <c r="Y59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3">
         <v>8227900</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>7018400</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF59" s="3">
         <v>7701900</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH59" s="3">
         <v>6037900</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>6679200</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL59" s="3">
         <v>5213900</v>
       </c>
-      <c r="AK59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN59" s="3">
         <v>6112000</v>
       </c>
-      <c r="AM59" s="3" t="s">
+      <c r="AO59" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35712100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>35687000</v>
+      </c>
+      <c r="F60" s="3">
         <v>35745200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>32897800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>34885600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>37582000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>34849500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>35090100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>36636500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>35081500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>37434500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>37255500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>33710600</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>5</v>
       </c>
@@ -6028,92 +6306,98 @@
       <c r="Y60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="Z60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB60" s="3">
         <v>26410300</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD60" s="3">
         <v>24760900</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF60" s="3">
         <v>19911800</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH60" s="3">
         <v>17311100</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>16817500</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL60" s="3">
         <v>14997600</v>
       </c>
-      <c r="AK60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN60" s="3">
         <v>15036500</v>
       </c>
-      <c r="AM60" s="3" t="s">
+      <c r="AO60" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30340500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>30319100</v>
+      </c>
+      <c r="F61" s="3">
         <v>31283600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>28791600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>27991500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>30155000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>27719900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>27911300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>27784900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>26605600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>24015300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>23900500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>24917200</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -6142,91 +6426,97 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>18064500</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>18501200</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>7103300</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>7347800</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>7905500</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
         <v>9213800</v>
       </c>
-      <c r="AK61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3">
         <v>4615400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10814800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>10807200</v>
+      </c>
+      <c r="F62" s="3">
         <v>11517300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>10599900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>11570600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>12464900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>12634700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>12722000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>16679600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>15971600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>17234700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>17152300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>16682700</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>5</v>
       </c>
@@ -6254,50 +6544,56 @@
       <c r="Y62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3">
         <v>23400700</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>22068100</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="3">
         <v>20706700</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH62" s="3">
         <v>19544400</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>19458700</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL62" s="3">
         <v>17915900</v>
       </c>
-      <c r="AK62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN62" s="3">
         <v>17580200</v>
       </c>
-      <c r="AM62" s="3" t="s">
+      <c r="AO62" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6409,8 +6705,14 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6522,8 +6824,14 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6635,50 +6943,56 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>85814300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>85753800</v>
+      </c>
+      <c r="F66" s="3">
         <v>87727500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>80739300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>82723900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>89117800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>83541200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>84118000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>89524700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>85725000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>87255500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>86838300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>83404900</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>5</v>
       </c>
@@ -6706,50 +7020,56 @@
       <c r="Y66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3">
         <v>69952400</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3">
         <v>67344200</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF66" s="3">
         <v>49690100</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH66" s="3">
         <v>45841500</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>45761500</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL66" s="3">
         <v>43746400</v>
       </c>
-      <c r="AK66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN66" s="3">
         <v>39004500</v>
       </c>
-      <c r="AM66" s="3" t="s">
+      <c r="AO66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6789,8 +7109,10 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6902,8 +7224,14 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7015,8 +7343,14 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7128,8 +7462,14 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7241,50 +7581,56 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12772100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>12763100</v>
+      </c>
+      <c r="F72" s="3">
         <v>6691700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>6158700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>12993100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>13997300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>7786300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>7840100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>16771300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>16059500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>9257600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>9213400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>15052900</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
@@ -7312,50 +7658,56 @@
       <c r="Y72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>38341200</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>35396700</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3">
         <v>34086400</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="3">
         <v>29060800</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>28350400</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL72" s="3">
         <v>25598200</v>
       </c>
-      <c r="AK72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN72" s="3">
         <v>25760400</v>
       </c>
-      <c r="AM72" s="3" t="s">
+      <c r="AO72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7467,8 +7819,14 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7580,8 +7938,14 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7693,50 +8057,56 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>79220400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>79164600</v>
+      </c>
+      <c r="F76" s="3">
         <v>76682300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>70573900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>69900600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>75303400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>69436400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>69915800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>67444500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>64581900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>63009800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>62708600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>58898200</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>5</v>
       </c>
@@ -7764,50 +8134,56 @@
       <c r="Y76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="3">
         <v>42710900</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD76" s="3">
         <v>39618800</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF76" s="3">
         <v>38199400</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH76" s="3">
         <v>32929000</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>32502900</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL76" s="3">
         <v>30113100</v>
       </c>
-      <c r="AK76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN76" s="3">
         <v>30980400</v>
       </c>
-      <c r="AM76" s="3" t="s">
+      <c r="AO76" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7919,126 +8295,138 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8078,80 +8466,86 @@
       <c r="O81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>7107500</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>7314400</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>5607400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>4169100</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>569500</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="3">
         <v>4556400</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD81" s="3">
         <v>3844500</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF81" s="3">
         <v>3962700</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH81" s="3">
         <v>3298400</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>3633000</v>
       </c>
-      <c r="AI81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL81" s="3">
         <v>2386500</v>
       </c>
-      <c r="AK81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN81" s="3">
         <v>2664500</v>
       </c>
-      <c r="AM81" s="3" t="s">
+      <c r="AO81" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8191,121 +8585,129 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1344300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1448200</v>
+      </c>
+      <c r="F83" s="3">
         <v>1681100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1692700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1318100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1262200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1566600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1559100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1216200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1124700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1447300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1538000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>780200</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>6320300</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>6034300</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>3203400</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>2781000</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF83" s="3">
         <v>1462100</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH83" s="3">
         <v>1170500</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>1532600</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL83" s="3">
         <v>1133200</v>
       </c>
-      <c r="AK83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN83" s="3">
         <v>1526000</v>
       </c>
-      <c r="AM83" s="3" t="s">
+      <c r="AO83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8417,8 +8819,14 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8530,8 +8938,14 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8643,8 +9057,14 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8756,8 +9176,14 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8869,121 +9295,133 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6453600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>6449000</v>
+      </c>
+      <c r="F89" s="3">
         <v>4627700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>4259100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>6025500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>6491200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>3902300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>3929200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>6438600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>6165300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>3684500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>3666900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>5646600</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>20216300</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>10868700</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>8707700</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>4927900</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>6303700</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH89" s="3">
         <v>3470800</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>5345200</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL89" s="3">
         <v>2542400</v>
       </c>
-      <c r="AK89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN89" s="3">
         <v>5407700</v>
       </c>
-      <c r="AM89" s="3" t="s">
+      <c r="AO89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9023,121 +9461,129 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-872400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-871800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1385800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1275400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1028600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1108100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1461500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1471600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1792300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1716200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1945400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1936100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1343900</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1197000</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-1978800</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-2034800</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-1314000</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-1961200</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-1038700</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-1257800</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-861700</v>
       </c>
-      <c r="AK91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-1928600</v>
       </c>
-      <c r="AM91" s="3" t="s">
+      <c r="AO91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9249,8 +9695,14 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9362,121 +9814,133 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1284500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1283600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1439800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1325100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1747100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1882100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1695100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1706800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2329500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2230600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-2235300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-2224600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2071200</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-17322800</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-2931400</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-2896300</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-3985600</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-2602400</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-1360400</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-8053600</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-1603300</v>
       </c>
-      <c r="AK94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN94" s="3">
         <v>-1367500</v>
       </c>
-      <c r="AM94" s="3" t="s">
+      <c r="AO94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9516,121 +9980,129 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1603300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1602100</v>
+      </c>
+      <c r="F96" s="3">
         <v>2192600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>2017900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>1421000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>1530800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>2007400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>2021300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>1518700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>1454300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>1912100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>1903000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>1338600</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-4510900</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-2427700</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1367000</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-2837500</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1190000</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-1876500</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-902100</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-1465300</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-826400</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9742,8 +10214,14 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9855,8 +10333,14 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9968,343 +10452,367 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4772200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-4768900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-3973600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-3657000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2987400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-3218300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2649200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2667500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2976100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2849800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2190000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-2179500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-3660900</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>-16430600</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>7383800</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-3917800</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-1621100</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-3320400</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-1664600</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-2373000</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL100" s="3">
         <v>4794300</v>
       </c>
-      <c r="AK100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN100" s="3">
         <v>-3366500</v>
       </c>
-      <c r="AM100" s="3" t="s">
+      <c r="AO100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>34600</v>
+      </c>
+      <c r="F101" s="3">
         <v>9600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>9700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-21600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-20600</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-127700</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-127100</v>
       </c>
       <c r="J101" s="3">
         <v>-127700</v>
       </c>
       <c r="K101" s="3">
+        <v>-127100</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-127700</v>
+      </c>
+      <c r="M101" s="3">
         <v>-117200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>153700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>163300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>212100</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>539900</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>-1049300</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="3">
         <v>28000</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
         <v>17600</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF101" s="3">
         <v>45000</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH101" s="3">
         <v>31800</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-30300</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-97600</v>
       </c>
-      <c r="AK101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AM101" s="3" t="s">
+      <c r="AO101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>319900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>319700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-854400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-786300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1323100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1425400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-432300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-435300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1111400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1064200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-868400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-864300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-213200</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>-12997300</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>14271800</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>1921600</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-661100</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>425800</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="3">
         <v>477600</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-5270000</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL102" s="3">
         <v>5585300</v>
       </c>
-      <c r="AK102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN102" s="3">
         <v>672600</v>
       </c>
-      <c r="AM102" s="3" t="s">
+      <c r="AO102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
